--- a/population.csv.xlsx
+++ b/population.csv.xlsx
@@ -8,19 +8,60 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Project\Indian Population Data Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D81E42AE-0307-4A3F-B737-0930F4968394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BD8FB3-6457-447E-BB0F-5D7F160F7A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB82829B-6F12-444B-8421-B58D62F0B729}"/>
   </bookViews>
   <sheets>
     <sheet name="population" sheetId="1" r:id="rId1"/>
+    <sheet name="Summery" sheetId="2" r:id="rId2"/>
+    <sheet name="PivotTable" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="22" r:id="rId5"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="96">
   <si>
     <t>Rank</t>
   </si>
@@ -43,9 +84,6 @@
     <t>Females</t>
   </si>
   <si>
-    <t>Sex Ratio</t>
-  </si>
-  <si>
     <t>Literacy Rate (%)</t>
   </si>
   <si>
@@ -257,6 +295,60 @@
   </si>
   <si>
     <t>Kavaratti</t>
+  </si>
+  <si>
+    <t>Gender Ratio</t>
+  </si>
+  <si>
+    <t>% of Total Max Population</t>
+  </si>
+  <si>
+    <t>% of Total Min Population</t>
+  </si>
+  <si>
+    <t>% of Total Avg Population</t>
+  </si>
+  <si>
+    <t>Max Gender Ratio</t>
+  </si>
+  <si>
+    <t>Min Gender Ratio</t>
+  </si>
+  <si>
+    <t>Avg Gender Ratio</t>
+  </si>
+  <si>
+    <t>Max Literacy Rate (%)</t>
+  </si>
+  <si>
+    <t>Min Literacy Rate (%)</t>
+  </si>
+  <si>
+    <t>Avg Literacy Rate (%)</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Rural Population</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>(Multiple Items)</t>
+  </si>
+  <si>
+    <t>Sum of Females</t>
+  </si>
+  <si>
+    <t>Sum of % of Total Population</t>
+  </si>
+  <si>
+    <t>Sum of Urban Population</t>
   </si>
 </sst>
 </file>
@@ -399,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,6 +683,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -767,13 +871,30 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -830,6 +951,2983 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="FAHIM" refreshedDate="46196.530847800925" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="39" xr:uid="{12F72F36-4652-4247-896A-88F09ED40986}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:N1048576" sheet="population"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="Rank" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="35"/>
+    </cacheField>
+    <cacheField name="State" numFmtId="0">
+      <sharedItems containsBlank="1" count="36">
+        <s v="Uttar Pradesh"/>
+        <s v="Maharashtra"/>
+        <s v="Bihar"/>
+        <s v="West Bengal"/>
+        <s v="Andhra Pradesh"/>
+        <s v="Madhya Pradesh"/>
+        <s v="Tamil Nadu"/>
+        <s v="Rajasthan"/>
+        <s v="Karnataka"/>
+        <s v="Gujarat"/>
+        <s v="Odisha"/>
+        <s v="Kerala"/>
+        <s v="Jharkhand"/>
+        <s v="Assam"/>
+        <s v="Punjab"/>
+        <s v="Chhattisgarh"/>
+        <s v="Haryana"/>
+        <s v="Delhi"/>
+        <s v="Jammu and Kashmir"/>
+        <s v="Uttarakhand"/>
+        <s v="Himachal Pradesh"/>
+        <s v="Tripura"/>
+        <s v="Meghalaya"/>
+        <s v="Manipur"/>
+        <s v="Nagaland"/>
+        <s v="Goa"/>
+        <s v="Arunachal Pradesh"/>
+        <s v="Puducherry"/>
+        <s v="Mizoram"/>
+        <s v="Chandigarh"/>
+        <s v="Sikkim"/>
+        <s v="Andaman and Nicobar Islands"/>
+        <s v="Dadra and Nagar Haveli"/>
+        <s v="Daman and Diu"/>
+        <s v="Lakshadweep"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Capital" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Population" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="64473" maxValue="199812341"/>
+    </cacheField>
+    <cacheField name="% of Total Population" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.01" maxValue="16.5"/>
+    </cacheField>
+    <cacheField name="Males" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="33123" maxValue="104480510"/>
+    </cacheField>
+    <cacheField name="Females" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="31350" maxValue="95331831"/>
+    </cacheField>
+    <cacheField name="Gender Ratio" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="618" maxValue="1084" count="34">
+        <n v="912"/>
+        <n v="929"/>
+        <n v="918"/>
+        <n v="950"/>
+        <n v="993"/>
+        <n v="931"/>
+        <n v="996"/>
+        <n v="928"/>
+        <n v="973"/>
+        <n v="919"/>
+        <n v="979"/>
+        <n v="1084"/>
+        <n v="948"/>
+        <n v="958"/>
+        <n v="895"/>
+        <n v="991"/>
+        <n v="879"/>
+        <n v="868"/>
+        <n v="889"/>
+        <n v="963"/>
+        <n v="972"/>
+        <n v="960"/>
+        <n v="989"/>
+        <n v="992"/>
+        <n v="938"/>
+        <n v="1037"/>
+        <n v="976"/>
+        <n v="818"/>
+        <n v="890"/>
+        <n v="876"/>
+        <n v="774"/>
+        <n v="618"/>
+        <n v="946"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Literacy Rate (%)" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="61.8" maxValue="94" count="36">
+        <n v="67.680000000000007"/>
+        <n v="82.34"/>
+        <n v="61.8"/>
+        <n v="76.260000000000005"/>
+        <n v="67.02"/>
+        <n v="69.319999999999993"/>
+        <n v="80.09"/>
+        <n v="66.11"/>
+        <n v="75.36"/>
+        <n v="78.03"/>
+        <n v="72.87"/>
+        <n v="94"/>
+        <n v="66.41"/>
+        <n v="72.19"/>
+        <n v="75.84"/>
+        <n v="70.28"/>
+        <n v="75.55"/>
+        <n v="86.21"/>
+        <n v="67.16"/>
+        <n v="79.63"/>
+        <n v="82.8"/>
+        <n v="87.22"/>
+        <n v="74.430000000000007"/>
+        <n v="79.209999999999994"/>
+        <n v="79.55"/>
+        <n v="88.7"/>
+        <n v="65.38"/>
+        <n v="85.85"/>
+        <n v="91.33"/>
+        <n v="86.05"/>
+        <n v="81.42"/>
+        <n v="86.63"/>
+        <n v="76.239999999999995"/>
+        <n v="87.1"/>
+        <n v="91.85"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Rural Population" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="14121" maxValue="155111022"/>
+    </cacheField>
+    <cacheField name="Urban Population" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="50308" maxValue="50827531"/>
+    </cacheField>
+    <cacheField name="Area (km*km)" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="32" maxValue="342239"/>
+    </cacheField>
+    <cacheField name="Density (1/km*km)" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="17" maxValue="11297"/>
+    </cacheField>
+    <cacheField name="Decadal Growth (%)" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="5.0000000000000001E-3" maxValue="0.55500000000000005"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="FAHIM" refreshedDate="46196.532465509263" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="35" xr:uid="{1CAE6F5E-4A68-4493-B8F4-898DFE1F623D}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:N36" sheet="population"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="Rank" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="35" count="35">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="State" numFmtId="0">
+      <sharedItems count="35">
+        <s v="Uttar Pradesh"/>
+        <s v="Maharashtra"/>
+        <s v="Bihar"/>
+        <s v="West Bengal"/>
+        <s v="Andhra Pradesh"/>
+        <s v="Madhya Pradesh"/>
+        <s v="Tamil Nadu"/>
+        <s v="Rajasthan"/>
+        <s v="Karnataka"/>
+        <s v="Gujarat"/>
+        <s v="Odisha"/>
+        <s v="Kerala"/>
+        <s v="Jharkhand"/>
+        <s v="Assam"/>
+        <s v="Punjab"/>
+        <s v="Chhattisgarh"/>
+        <s v="Haryana"/>
+        <s v="Delhi"/>
+        <s v="Jammu and Kashmir"/>
+        <s v="Uttarakhand"/>
+        <s v="Himachal Pradesh"/>
+        <s v="Tripura"/>
+        <s v="Meghalaya"/>
+        <s v="Manipur"/>
+        <s v="Nagaland"/>
+        <s v="Goa"/>
+        <s v="Arunachal Pradesh"/>
+        <s v="Puducherry"/>
+        <s v="Mizoram"/>
+        <s v="Chandigarh"/>
+        <s v="Sikkim"/>
+        <s v="Andaman and Nicobar Islands"/>
+        <s v="Dadra and Nagar Haveli"/>
+        <s v="Daman and Diu"/>
+        <s v="Lakshadweep"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Capital" numFmtId="0">
+      <sharedItems count="33">
+        <s v="Lucknow"/>
+        <s v="Mumbai"/>
+        <s v="Patna"/>
+        <s v="Kolkata"/>
+        <s v="Hyderabad"/>
+        <s v="Bhopal"/>
+        <s v="Chennai"/>
+        <s v="Jaipur"/>
+        <s v="Bengaluru"/>
+        <s v="Gandhinagar"/>
+        <s v="Bhubaneshwar"/>
+        <s v="Thiruvananthapuram"/>
+        <s v="Ranchi"/>
+        <s v="Dispur"/>
+        <s v="Chandigarh"/>
+        <s v="Raipur"/>
+        <s v="Delhi"/>
+        <s v="Jammu and Kashmir"/>
+        <s v="Dehradun"/>
+        <s v="Shimla"/>
+        <s v="Agartala"/>
+        <s v="Shillong"/>
+        <s v="Imphal"/>
+        <s v="Kohima"/>
+        <s v="Panaji"/>
+        <s v="Itanagar"/>
+        <s v="Pondicherry"/>
+        <s v="Aizawl"/>
+        <s v="Gangtok"/>
+        <s v="Port Blair"/>
+        <s v="Silvassa"/>
+        <s v="Daman"/>
+        <s v="Kavaratti"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Population" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="64473" maxValue="199812341"/>
+    </cacheField>
+    <cacheField name="% of Total Population" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.01" maxValue="16.5" count="33">
+        <n v="16.5"/>
+        <n v="9.2799999999999994"/>
+        <n v="8.6"/>
+        <n v="7.54"/>
+        <n v="6.99"/>
+        <n v="6"/>
+        <n v="5.96"/>
+        <n v="5.66"/>
+        <n v="5.05"/>
+        <n v="4.99"/>
+        <n v="3.47"/>
+        <n v="2.76"/>
+        <n v="2.72"/>
+        <n v="2.58"/>
+        <n v="2.29"/>
+        <n v="2.11"/>
+        <n v="2.09"/>
+        <n v="1.39"/>
+        <n v="1.04"/>
+        <n v="0.83"/>
+        <n v="0.56999999999999995"/>
+        <n v="0.3"/>
+        <n v="0.25"/>
+        <n v="0.21"/>
+        <n v="0.16"/>
+        <n v="0.12"/>
+        <n v="0.11"/>
+        <n v="0.1"/>
+        <n v="0.09"/>
+        <n v="0.05"/>
+        <n v="0.03"/>
+        <n v="0.02"/>
+        <n v="0.01"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Males" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="33123" maxValue="104480510"/>
+    </cacheField>
+    <cacheField name="Females" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="31350" maxValue="95331831"/>
+    </cacheField>
+    <cacheField name="Gender Ratio" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="618" maxValue="1084" count="33">
+        <n v="912"/>
+        <n v="929"/>
+        <n v="918"/>
+        <n v="950"/>
+        <n v="993"/>
+        <n v="931"/>
+        <n v="996"/>
+        <n v="928"/>
+        <n v="973"/>
+        <n v="919"/>
+        <n v="979"/>
+        <n v="1084"/>
+        <n v="948"/>
+        <n v="958"/>
+        <n v="895"/>
+        <n v="991"/>
+        <n v="879"/>
+        <n v="868"/>
+        <n v="889"/>
+        <n v="963"/>
+        <n v="972"/>
+        <n v="960"/>
+        <n v="989"/>
+        <n v="992"/>
+        <n v="938"/>
+        <n v="1037"/>
+        <n v="976"/>
+        <n v="818"/>
+        <n v="890"/>
+        <n v="876"/>
+        <n v="774"/>
+        <n v="618"/>
+        <n v="946"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Literacy Rate (%)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="61.8" maxValue="94" count="35">
+        <n v="67.680000000000007"/>
+        <n v="82.34"/>
+        <n v="61.8"/>
+        <n v="76.260000000000005"/>
+        <n v="67.02"/>
+        <n v="69.319999999999993"/>
+        <n v="80.09"/>
+        <n v="66.11"/>
+        <n v="75.36"/>
+        <n v="78.03"/>
+        <n v="72.87"/>
+        <n v="94"/>
+        <n v="66.41"/>
+        <n v="72.19"/>
+        <n v="75.84"/>
+        <n v="70.28"/>
+        <n v="75.55"/>
+        <n v="86.21"/>
+        <n v="67.16"/>
+        <n v="79.63"/>
+        <n v="82.8"/>
+        <n v="87.22"/>
+        <n v="74.430000000000007"/>
+        <n v="79.209999999999994"/>
+        <n v="79.55"/>
+        <n v="88.7"/>
+        <n v="65.38"/>
+        <n v="85.85"/>
+        <n v="91.33"/>
+        <n v="86.05"/>
+        <n v="81.42"/>
+        <n v="86.63"/>
+        <n v="76.239999999999995"/>
+        <n v="87.1"/>
+        <n v="91.85"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Rural Population" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="14121" maxValue="155111022" count="35">
+        <n v="155111022"/>
+        <n v="61545441"/>
+        <n v="92075028"/>
+        <n v="62213676"/>
+        <n v="56361702"/>
+        <n v="52537899"/>
+        <n v="37189229"/>
+        <n v="51540236"/>
+        <n v="37552529"/>
+        <n v="34670817"/>
+        <n v="34951234"/>
+        <n v="17445506"/>
+        <n v="25036946"/>
+        <n v="26780526"/>
+        <n v="17316800"/>
+        <n v="19603658"/>
+        <n v="16531493"/>
+        <n v="944727"/>
+        <n v="9134820"/>
+        <n v="7025583"/>
+        <n v="6167805"/>
+        <n v="2710051"/>
+        <n v="2368971"/>
+        <n v="1899624"/>
+        <n v="1406861"/>
+        <n v="551414"/>
+        <n v="1069165"/>
+        <n v="394341"/>
+        <n v="529037"/>
+        <n v="29004"/>
+        <n v="455962"/>
+        <n v="244411"/>
+        <n v="183024"/>
+        <n v="60331"/>
+        <n v="14121"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Urban Population" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50308" maxValue="50827531" count="35">
+        <n v="44470455"/>
+        <n v="50827531"/>
+        <n v="11729609"/>
+        <n v="29134060"/>
+        <n v="28219075"/>
+        <n v="20059666"/>
+        <n v="34949729"/>
+        <n v="17080776"/>
+        <n v="23578175"/>
+        <n v="25712811"/>
+        <n v="6996124"/>
+        <n v="15932171"/>
+        <n v="7929292"/>
+        <n v="4388756"/>
+        <n v="10387436"/>
+        <n v="5936538"/>
+        <n v="8821588"/>
+        <n v="12905780"/>
+        <n v="3414106"/>
+        <n v="3091169"/>
+        <n v="688704"/>
+        <n v="960981"/>
+        <n v="595036"/>
+        <n v="822132"/>
+        <n v="573741"/>
+        <n v="906309"/>
+        <n v="313446"/>
+        <n v="850123"/>
+        <n v="561997"/>
+        <n v="1025682"/>
+        <n v="151726"/>
+        <n v="135533"/>
+        <n v="159829"/>
+        <n v="182580"/>
+        <n v="50308"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Area (km*km)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="32" maxValue="342239" count="35">
+        <n v="240928"/>
+        <n v="307713"/>
+        <n v="94163"/>
+        <n v="88752"/>
+        <n v="275045"/>
+        <n v="308245"/>
+        <n v="130058"/>
+        <n v="342239"/>
+        <n v="191791"/>
+        <n v="196024"/>
+        <n v="155707"/>
+        <n v="38863"/>
+        <n v="79714"/>
+        <n v="78438"/>
+        <n v="50362"/>
+        <n v="135191"/>
+        <n v="44212"/>
+        <n v="1484"/>
+        <n v="222236"/>
+        <n v="53483"/>
+        <n v="55673"/>
+        <n v="10486"/>
+        <n v="22429"/>
+        <n v="22327"/>
+        <n v="16579"/>
+        <n v="3702"/>
+        <n v="83743"/>
+        <n v="479"/>
+        <n v="21081"/>
+        <n v="114"/>
+        <n v="7096"/>
+        <n v="8249"/>
+        <n v="491"/>
+        <n v="112"/>
+        <n v="32"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Density (1/km*km)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="17" maxValue="11297" count="33">
+        <n v="828"/>
+        <n v="365"/>
+        <n v="1102"/>
+        <n v="1030"/>
+        <n v="308"/>
+        <n v="236"/>
+        <n v="555"/>
+        <n v="201"/>
+        <n v="319"/>
+        <n v="269"/>
+        <n v="859"/>
+        <n v="414"/>
+        <n v="397"/>
+        <n v="550"/>
+        <n v="189"/>
+        <n v="573"/>
+        <n v="11297"/>
+        <n v="56"/>
+        <n v="123"/>
+        <n v="350"/>
+        <n v="132"/>
+        <n v="122"/>
+        <n v="119"/>
+        <n v="394"/>
+        <n v="17"/>
+        <n v="2598"/>
+        <n v="52"/>
+        <n v="9252"/>
+        <n v="86"/>
+        <n v="46"/>
+        <n v="698"/>
+        <n v="2169"/>
+        <n v="2013"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Decadal Growth (%)" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.0000000000000001E-3" maxValue="0.55500000000000005"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="39">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="Lucknow"/>
+    <n v="199812341"/>
+    <n v="16.5"/>
+    <n v="104480510"/>
+    <n v="95331831"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="155111022"/>
+    <n v="44470455"/>
+    <n v="240928"/>
+    <n v="828"/>
+    <n v="0.20100000000000001"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <s v="Mumbai"/>
+    <n v="112374333"/>
+    <n v="9.2799999999999994"/>
+    <n v="58243056"/>
+    <n v="54131277"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="61545441"/>
+    <n v="50827531"/>
+    <n v="307713"/>
+    <n v="365"/>
+    <n v="0.16"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <s v="Patna"/>
+    <n v="104099452"/>
+    <n v="8.6"/>
+    <n v="54278157"/>
+    <n v="49821295"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="92075028"/>
+    <n v="11729609"/>
+    <n v="94163"/>
+    <n v="1102"/>
+    <n v="0.251"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <s v="Kolkata"/>
+    <n v="91276115"/>
+    <n v="7.54"/>
+    <n v="46809027"/>
+    <n v="44467088"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="62213676"/>
+    <n v="29134060"/>
+    <n v="88752"/>
+    <n v="1030"/>
+    <n v="0.13900000000000001"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <s v="Hyderabad"/>
+    <n v="84580777"/>
+    <n v="6.99"/>
+    <n v="42442146"/>
+    <n v="42138631"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="56361702"/>
+    <n v="28219075"/>
+    <n v="275045"/>
+    <n v="308"/>
+    <n v="0.10979999999999999"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="5"/>
+    <s v="Bhopal"/>
+    <n v="72626809"/>
+    <n v="6"/>
+    <n v="37612306"/>
+    <n v="35014503"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="52537899"/>
+    <n v="20059666"/>
+    <n v="308245"/>
+    <n v="236"/>
+    <n v="0.20300000000000001"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="6"/>
+    <s v="Chennai"/>
+    <n v="72147030"/>
+    <n v="5.96"/>
+    <n v="36137975"/>
+    <n v="36009055"/>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="37189229"/>
+    <n v="34949729"/>
+    <n v="130058"/>
+    <n v="555"/>
+    <n v="0.156"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="7"/>
+    <s v="Jaipur"/>
+    <n v="68548437"/>
+    <n v="5.66"/>
+    <n v="35550997"/>
+    <n v="32997440"/>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="51540236"/>
+    <n v="17080776"/>
+    <n v="342239"/>
+    <n v="201"/>
+    <n v="0.214"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="8"/>
+    <s v="Bengaluru"/>
+    <n v="61095297"/>
+    <n v="5.05"/>
+    <n v="30966657"/>
+    <n v="30128640"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="37552529"/>
+    <n v="23578175"/>
+    <n v="191791"/>
+    <n v="319"/>
+    <n v="0.157"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="9"/>
+    <s v="Gandhinagar"/>
+    <n v="60439692"/>
+    <n v="4.99"/>
+    <n v="31491260"/>
+    <n v="28948432"/>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="34670817"/>
+    <n v="25712811"/>
+    <n v="196024"/>
+    <n v="308"/>
+    <n v="0.192"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="10"/>
+    <s v="Bhubaneshwar"/>
+    <n v="41974218"/>
+    <n v="3.47"/>
+    <n v="21212136"/>
+    <n v="20762082"/>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="34951234"/>
+    <n v="6996124"/>
+    <n v="155707"/>
+    <n v="269"/>
+    <n v="0.14000000000000001"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="11"/>
+    <s v="Thiruvananthapuram"/>
+    <n v="33406061"/>
+    <n v="2.76"/>
+    <n v="16027412"/>
+    <n v="17378649"/>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="17445506"/>
+    <n v="15932171"/>
+    <n v="38863"/>
+    <n v="859"/>
+    <n v="4.9000000000000002E-2"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="12"/>
+    <s v="Ranchi"/>
+    <n v="32988134"/>
+    <n v="2.72"/>
+    <n v="16930315"/>
+    <n v="16057819"/>
+    <x v="12"/>
+    <x v="12"/>
+    <n v="25036946"/>
+    <n v="7929292"/>
+    <n v="79714"/>
+    <n v="414"/>
+    <n v="0.223"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="13"/>
+    <s v="Dispur"/>
+    <n v="31205576"/>
+    <n v="2.58"/>
+    <n v="15939443"/>
+    <n v="15266133"/>
+    <x v="13"/>
+    <x v="13"/>
+    <n v="26780526"/>
+    <n v="4388756"/>
+    <n v="78438"/>
+    <n v="397"/>
+    <n v="0.16900000000000001"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="14"/>
+    <s v="Chandigarh"/>
+    <n v="27743338"/>
+    <n v="2.29"/>
+    <n v="14639465"/>
+    <n v="13103873"/>
+    <x v="14"/>
+    <x v="14"/>
+    <n v="17316800"/>
+    <n v="10387436"/>
+    <n v="50362"/>
+    <n v="550"/>
+    <n v="0.13700000000000001"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <x v="15"/>
+    <s v="Raipur"/>
+    <n v="25545198"/>
+    <n v="2.11"/>
+    <n v="12832895"/>
+    <n v="12712303"/>
+    <x v="15"/>
+    <x v="15"/>
+    <n v="19603658"/>
+    <n v="5936538"/>
+    <n v="135191"/>
+    <n v="189"/>
+    <n v="0.22600000000000001"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <x v="16"/>
+    <s v="Chandigarh"/>
+    <n v="25351462"/>
+    <n v="2.09"/>
+    <n v="13494734"/>
+    <n v="11856728"/>
+    <x v="16"/>
+    <x v="16"/>
+    <n v="16531493"/>
+    <n v="8821588"/>
+    <n v="44212"/>
+    <n v="573"/>
+    <n v="0.19900000000000001"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <x v="17"/>
+    <s v="Delhi"/>
+    <n v="16787941"/>
+    <n v="1.39"/>
+    <n v="8887326"/>
+    <n v="7800615"/>
+    <x v="17"/>
+    <x v="17"/>
+    <n v="944727"/>
+    <n v="12905780"/>
+    <n v="1484"/>
+    <n v="11297"/>
+    <n v="0.21"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <x v="18"/>
+    <s v="Jammu and Kashmir"/>
+    <n v="12541302"/>
+    <n v="1.04"/>
+    <n v="6640662"/>
+    <n v="5900640"/>
+    <x v="18"/>
+    <x v="18"/>
+    <n v="9134820"/>
+    <n v="3414106"/>
+    <n v="222236"/>
+    <n v="56"/>
+    <n v="0.23699999999999999"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <x v="19"/>
+    <s v="Dehradun"/>
+    <n v="10086292"/>
+    <n v="0.83"/>
+    <n v="5137773"/>
+    <n v="4948519"/>
+    <x v="19"/>
+    <x v="19"/>
+    <n v="7025583"/>
+    <n v="3091169"/>
+    <n v="53483"/>
+    <n v="189"/>
+    <n v="0.192"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <x v="20"/>
+    <s v="Shimla"/>
+    <n v="6864602"/>
+    <n v="0.56999999999999995"/>
+    <n v="3481873"/>
+    <n v="3382729"/>
+    <x v="20"/>
+    <x v="20"/>
+    <n v="6167805"/>
+    <n v="688704"/>
+    <n v="55673"/>
+    <n v="123"/>
+    <n v="0.128"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <x v="21"/>
+    <s v="Agartala"/>
+    <n v="3673917"/>
+    <n v="0.3"/>
+    <n v="1874376"/>
+    <n v="1799541"/>
+    <x v="21"/>
+    <x v="21"/>
+    <n v="2710051"/>
+    <n v="960981"/>
+    <n v="10486"/>
+    <n v="350"/>
+    <n v="0.14699999999999999"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <x v="22"/>
+    <s v="Shillong"/>
+    <n v="2966889"/>
+    <n v="0.25"/>
+    <n v="1491832"/>
+    <n v="1475057"/>
+    <x v="22"/>
+    <x v="22"/>
+    <n v="2368971"/>
+    <n v="595036"/>
+    <n v="22429"/>
+    <n v="132"/>
+    <n v="0.27800000000000002"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <x v="23"/>
+    <s v="Imphal"/>
+    <n v="2721756"/>
+    <n v="0.21"/>
+    <n v="1290171"/>
+    <n v="1280219"/>
+    <x v="23"/>
+    <x v="23"/>
+    <n v="1899624"/>
+    <n v="822132"/>
+    <n v="22327"/>
+    <n v="122"/>
+    <n v="0.187"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <x v="24"/>
+    <s v="Kohima"/>
+    <n v="1978502"/>
+    <n v="0.16"/>
+    <n v="1024649"/>
+    <n v="953853"/>
+    <x v="5"/>
+    <x v="24"/>
+    <n v="1406861"/>
+    <n v="573741"/>
+    <n v="16579"/>
+    <n v="119"/>
+    <n v="5.0000000000000001E-3"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <x v="25"/>
+    <s v="Panaji"/>
+    <n v="1458545"/>
+    <n v="0.12"/>
+    <n v="739140"/>
+    <n v="719405"/>
+    <x v="8"/>
+    <x v="25"/>
+    <n v="551414"/>
+    <n v="906309"/>
+    <n v="3702"/>
+    <n v="394"/>
+    <n v="8.2000000000000003E-2"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <x v="26"/>
+    <s v="Itanagar"/>
+    <n v="1383727"/>
+    <n v="0.11"/>
+    <n v="713912"/>
+    <n v="669815"/>
+    <x v="24"/>
+    <x v="26"/>
+    <n v="1069165"/>
+    <n v="313446"/>
+    <n v="83743"/>
+    <n v="17"/>
+    <n v="0.25900000000000001"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <x v="27"/>
+    <s v="Pondicherry"/>
+    <n v="1247953"/>
+    <n v="0.1"/>
+    <n v="612511"/>
+    <n v="635442"/>
+    <x v="25"/>
+    <x v="27"/>
+    <n v="394341"/>
+    <n v="850123"/>
+    <n v="479"/>
+    <n v="2598"/>
+    <n v="0.27700000000000002"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <x v="28"/>
+    <s v="Aizawl"/>
+    <n v="1097206"/>
+    <n v="0.09"/>
+    <n v="555339"/>
+    <n v="541867"/>
+    <x v="26"/>
+    <x v="28"/>
+    <n v="529037"/>
+    <n v="561997"/>
+    <n v="21081"/>
+    <n v="52"/>
+    <n v="0.22800000000000001"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <x v="29"/>
+    <s v="Chandigarh"/>
+    <n v="1055450"/>
+    <n v="0.09"/>
+    <n v="580663"/>
+    <n v="474787"/>
+    <x v="27"/>
+    <x v="29"/>
+    <n v="29004"/>
+    <n v="1025682"/>
+    <n v="114"/>
+    <n v="9252"/>
+    <n v="0.17100000000000001"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <x v="30"/>
+    <s v="Gangtok"/>
+    <n v="610577"/>
+    <n v="0.05"/>
+    <n v="323070"/>
+    <n v="287507"/>
+    <x v="28"/>
+    <x v="30"/>
+    <n v="455962"/>
+    <n v="151726"/>
+    <n v="7096"/>
+    <n v="86"/>
+    <n v="0.124"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <x v="31"/>
+    <s v="Port Blair"/>
+    <n v="380581"/>
+    <n v="0.03"/>
+    <n v="202871"/>
+    <n v="177710"/>
+    <x v="29"/>
+    <x v="31"/>
+    <n v="244411"/>
+    <n v="135533"/>
+    <n v="8249"/>
+    <n v="46"/>
+    <n v="6.7000000000000004E-2"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <x v="32"/>
+    <s v="Silvassa"/>
+    <n v="343709"/>
+    <n v="0.03"/>
+    <n v="193760"/>
+    <n v="149949"/>
+    <x v="30"/>
+    <x v="32"/>
+    <n v="183024"/>
+    <n v="159829"/>
+    <n v="491"/>
+    <n v="698"/>
+    <n v="0.55500000000000005"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <x v="33"/>
+    <s v="Daman"/>
+    <n v="243247"/>
+    <n v="0.02"/>
+    <n v="150301"/>
+    <n v="92946"/>
+    <x v="31"/>
+    <x v="33"/>
+    <n v="60331"/>
+    <n v="182580"/>
+    <n v="112"/>
+    <n v="2169"/>
+    <n v="0.53500000000000003"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <x v="34"/>
+    <s v="Kavaratti"/>
+    <n v="64473"/>
+    <n v="0.01"/>
+    <n v="33123"/>
+    <n v="31350"/>
+    <x v="32"/>
+    <x v="34"/>
+    <n v="14121"/>
+    <n v="50308"/>
+    <n v="32"/>
+    <n v="2013"/>
+    <n v="6.2E-2"/>
+  </r>
+  <r>
+    <m/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="33"/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="33"/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="33"/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="33"/>
+    <x v="35"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="35">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="199812341"/>
+    <x v="0"/>
+    <n v="104480510"/>
+    <n v="95331831"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0.20100000000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="112374333"/>
+    <x v="1"/>
+    <n v="58243056"/>
+    <n v="54131277"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.16"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="104099452"/>
+    <x v="2"/>
+    <n v="54278157"/>
+    <n v="49821295"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="0.251"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="91276115"/>
+    <x v="3"/>
+    <n v="46809027"/>
+    <n v="44467088"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="0.13900000000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="84580777"/>
+    <x v="4"/>
+    <n v="42442146"/>
+    <n v="42138631"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="0.10979999999999999"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="72626809"/>
+    <x v="5"/>
+    <n v="37612306"/>
+    <n v="35014503"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="0.20300000000000001"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="72147030"/>
+    <x v="6"/>
+    <n v="36137975"/>
+    <n v="36009055"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="0.156"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="68548437"/>
+    <x v="7"/>
+    <n v="35550997"/>
+    <n v="32997440"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="0.214"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="61095297"/>
+    <x v="8"/>
+    <n v="30966657"/>
+    <n v="30128640"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="0.157"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="60439692"/>
+    <x v="9"/>
+    <n v="31491260"/>
+    <n v="28948432"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="0.192"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="41974218"/>
+    <x v="10"/>
+    <n v="21212136"/>
+    <n v="20762082"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="10"/>
+    <x v="9"/>
+    <n v="0.14000000000000001"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="33406061"/>
+    <x v="11"/>
+    <n v="16027412"/>
+    <n v="17378649"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="11"/>
+    <x v="10"/>
+    <n v="4.9000000000000002E-2"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="12"/>
+    <n v="32988134"/>
+    <x v="12"/>
+    <n v="16930315"/>
+    <n v="16057819"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="12"/>
+    <x v="11"/>
+    <n v="0.223"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="13"/>
+    <n v="31205576"/>
+    <x v="13"/>
+    <n v="15939443"/>
+    <n v="15266133"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="13"/>
+    <x v="12"/>
+    <n v="0.16900000000000001"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="14"/>
+    <n v="27743338"/>
+    <x v="14"/>
+    <n v="14639465"/>
+    <n v="13103873"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="14"/>
+    <x v="13"/>
+    <n v="0.13700000000000001"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="15"/>
+    <n v="25545198"/>
+    <x v="15"/>
+    <n v="12832895"/>
+    <n v="12712303"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="15"/>
+    <x v="14"/>
+    <n v="0.22600000000000001"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="14"/>
+    <n v="25351462"/>
+    <x v="16"/>
+    <n v="13494734"/>
+    <n v="11856728"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="16"/>
+    <x v="15"/>
+    <n v="0.19900000000000001"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="16"/>
+    <n v="16787941"/>
+    <x v="17"/>
+    <n v="8887326"/>
+    <n v="7800615"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="17"/>
+    <x v="16"/>
+    <n v="0.21"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="17"/>
+    <n v="12541302"/>
+    <x v="18"/>
+    <n v="6640662"/>
+    <n v="5900640"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="18"/>
+    <x v="17"/>
+    <n v="0.23699999999999999"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="18"/>
+    <n v="10086292"/>
+    <x v="19"/>
+    <n v="5137773"/>
+    <n v="4948519"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="19"/>
+    <x v="14"/>
+    <n v="0.192"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <x v="20"/>
+    <x v="19"/>
+    <n v="6864602"/>
+    <x v="20"/>
+    <n v="3481873"/>
+    <n v="3382729"/>
+    <x v="20"/>
+    <x v="20"/>
+    <x v="20"/>
+    <x v="20"/>
+    <x v="20"/>
+    <x v="18"/>
+    <n v="0.128"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <x v="21"/>
+    <x v="20"/>
+    <n v="3673917"/>
+    <x v="21"/>
+    <n v="1874376"/>
+    <n v="1799541"/>
+    <x v="21"/>
+    <x v="21"/>
+    <x v="21"/>
+    <x v="21"/>
+    <x v="21"/>
+    <x v="19"/>
+    <n v="0.14699999999999999"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="22"/>
+    <x v="21"/>
+    <n v="2966889"/>
+    <x v="22"/>
+    <n v="1491832"/>
+    <n v="1475057"/>
+    <x v="22"/>
+    <x v="22"/>
+    <x v="22"/>
+    <x v="22"/>
+    <x v="22"/>
+    <x v="20"/>
+    <n v="0.27800000000000002"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="23"/>
+    <x v="22"/>
+    <n v="2721756"/>
+    <x v="23"/>
+    <n v="1290171"/>
+    <n v="1280219"/>
+    <x v="23"/>
+    <x v="23"/>
+    <x v="23"/>
+    <x v="23"/>
+    <x v="23"/>
+    <x v="21"/>
+    <n v="0.187"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="24"/>
+    <x v="23"/>
+    <n v="1978502"/>
+    <x v="24"/>
+    <n v="1024649"/>
+    <n v="953853"/>
+    <x v="5"/>
+    <x v="24"/>
+    <x v="24"/>
+    <x v="24"/>
+    <x v="24"/>
+    <x v="22"/>
+    <n v="5.0000000000000001E-3"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="25"/>
+    <x v="24"/>
+    <n v="1458545"/>
+    <x v="25"/>
+    <n v="739140"/>
+    <n v="719405"/>
+    <x v="8"/>
+    <x v="25"/>
+    <x v="25"/>
+    <x v="25"/>
+    <x v="25"/>
+    <x v="23"/>
+    <n v="8.2000000000000003E-2"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <x v="26"/>
+    <x v="25"/>
+    <n v="1383727"/>
+    <x v="26"/>
+    <n v="713912"/>
+    <n v="669815"/>
+    <x v="24"/>
+    <x v="26"/>
+    <x v="26"/>
+    <x v="26"/>
+    <x v="26"/>
+    <x v="24"/>
+    <n v="0.25900000000000001"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="27"/>
+    <x v="26"/>
+    <n v="1247953"/>
+    <x v="27"/>
+    <n v="612511"/>
+    <n v="635442"/>
+    <x v="25"/>
+    <x v="27"/>
+    <x v="27"/>
+    <x v="27"/>
+    <x v="27"/>
+    <x v="25"/>
+    <n v="0.27700000000000002"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="28"/>
+    <x v="27"/>
+    <n v="1097206"/>
+    <x v="28"/>
+    <n v="555339"/>
+    <n v="541867"/>
+    <x v="26"/>
+    <x v="28"/>
+    <x v="28"/>
+    <x v="28"/>
+    <x v="28"/>
+    <x v="26"/>
+    <n v="0.22800000000000001"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="29"/>
+    <x v="14"/>
+    <n v="1055450"/>
+    <x v="28"/>
+    <n v="580663"/>
+    <n v="474787"/>
+    <x v="27"/>
+    <x v="29"/>
+    <x v="29"/>
+    <x v="29"/>
+    <x v="29"/>
+    <x v="27"/>
+    <n v="0.17100000000000001"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="30"/>
+    <x v="28"/>
+    <n v="610577"/>
+    <x v="29"/>
+    <n v="323070"/>
+    <n v="287507"/>
+    <x v="28"/>
+    <x v="30"/>
+    <x v="30"/>
+    <x v="30"/>
+    <x v="30"/>
+    <x v="28"/>
+    <n v="0.124"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="31"/>
+    <x v="29"/>
+    <n v="380581"/>
+    <x v="30"/>
+    <n v="202871"/>
+    <n v="177710"/>
+    <x v="29"/>
+    <x v="31"/>
+    <x v="31"/>
+    <x v="31"/>
+    <x v="31"/>
+    <x v="29"/>
+    <n v="6.7000000000000004E-2"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="32"/>
+    <x v="30"/>
+    <n v="343709"/>
+    <x v="30"/>
+    <n v="193760"/>
+    <n v="149949"/>
+    <x v="30"/>
+    <x v="32"/>
+    <x v="32"/>
+    <x v="32"/>
+    <x v="32"/>
+    <x v="30"/>
+    <n v="0.55500000000000005"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <x v="33"/>
+    <x v="31"/>
+    <n v="243247"/>
+    <x v="31"/>
+    <n v="150301"/>
+    <n v="92946"/>
+    <x v="31"/>
+    <x v="33"/>
+    <x v="33"/>
+    <x v="33"/>
+    <x v="33"/>
+    <x v="31"/>
+    <n v="0.53500000000000003"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="34"/>
+    <x v="32"/>
+    <n v="64473"/>
+    <x v="32"/>
+    <n v="33123"/>
+    <n v="31350"/>
+    <x v="32"/>
+    <x v="34"/>
+    <x v="34"/>
+    <x v="34"/>
+    <x v="34"/>
+    <x v="32"/>
+    <n v="6.2E-2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F7B912B-B7BC-4364-BBA6-38B4B0148DFC}" name="PivotTable4" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L5:M76" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="36">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="34">
+        <item x="20"/>
+        <item x="27"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="31"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="32"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="30"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="36">
+        <item x="34"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="27"/>
+        <item x="32"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="21"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="26"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="34">
+        <item x="24"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item x="17"/>
+        <item x="28"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="18"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="30"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="71">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="11" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of % of Total Population" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{51E9E64C-34E6-49FF-ABC4-DCBA46C9B4F0}" name="PivotTable3" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H5:J39" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="36">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="34">
+        <item x="20"/>
+        <item x="27"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="31"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="32"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="30"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="34">
+        <item x="32"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="29"/>
+        <item x="28"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="34">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="4" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sum of Urban Population" fld="10" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283C2D54-EA66-46DD-A52C-DBEC61E2F94E}" name="PivotTable2" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0">
+      <items count="36">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="36">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="34">
+        <item x="20"/>
+        <item x="27"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="31"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="25"/>
+        <item x="7"/>
+        <item x="17"/>
+        <item x="32"/>
+        <item x="23"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="26"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="30"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="34">
+        <item x="31"/>
+        <item x="30"/>
+        <item x="27"/>
+        <item x="17"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="14"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="32"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="25"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="36">
+        <item x="2"/>
+        <item x="26"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="4"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="8"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="32"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="6"/>
+        <item x="30"/>
+        <item x="1"/>
+        <item x="20"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="17"/>
+        <item x="31"/>
+        <item x="33"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="28"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="36">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Females" fld="6" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3E7D3-975D-432E-ACA4-EC6B906FDDBE}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="37">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="35">
+        <item x="31"/>
+        <item x="30"/>
+        <item x="27"/>
+        <item x="17"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="14"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="32"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="25"/>
+        <item x="11"/>
+        <item x="33"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="37">
+        <item h="1" x="2"/>
+        <item h="1" x="26"/>
+        <item h="1" x="7"/>
+        <item h="1" x="12"/>
+        <item h="1" x="4"/>
+        <item h="1" x="18"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="15"/>
+        <item h="1" x="13"/>
+        <item h="1" x="10"/>
+        <item h="1" x="22"/>
+        <item h="1" x="8"/>
+        <item h="1" x="16"/>
+        <item x="14"/>
+        <item x="32"/>
+        <item h="1" x="3"/>
+        <item h="1" x="9"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item x="19"/>
+        <item h="1" x="6"/>
+        <item h="1" x="30"/>
+        <item h="1" x="1"/>
+        <item h="1" x="20"/>
+        <item h="1" x="27"/>
+        <item h="1" x="29"/>
+        <item h="1" x="17"/>
+        <item x="31"/>
+        <item h="1" x="33"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="28"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item h="1" x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1159,7 +4257,7 @@
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -1191,25 +4289,25 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -1217,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D2" s="3">
         <v>199812341</v>
@@ -1261,10 +4359,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>112374333</v>
@@ -1305,10 +4403,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>104099452</v>
@@ -1349,10 +4447,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D5" s="3">
         <v>91276115</v>
@@ -1393,10 +4491,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="3">
         <v>84580777</v>
@@ -1437,10 +4535,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="3">
         <v>72626809</v>
@@ -1481,10 +4579,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D8" s="3">
         <v>72147030</v>
@@ -1525,10 +4623,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>68548437</v>
@@ -1569,10 +4667,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D10" s="3">
         <v>61095297</v>
@@ -1613,10 +4711,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D11" s="3">
         <v>60439692</v>
@@ -1657,10 +4755,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D12" s="3">
         <v>41974218</v>
@@ -1701,10 +4799,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D13" s="3">
         <v>33406061</v>
@@ -1745,10 +4843,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="3">
         <v>32988134</v>
@@ -1789,10 +4887,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D15" s="3">
         <v>31205576</v>
@@ -1833,10 +4931,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D16" s="3">
         <v>27743338</v>
@@ -1877,10 +4975,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D17" s="3">
         <v>25545198</v>
@@ -1921,10 +5019,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3">
         <v>25351462</v>
@@ -1965,10 +5063,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3">
         <v>16787941</v>
@@ -2009,10 +5107,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3">
         <v>12541302</v>
@@ -2053,10 +5151,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D21" s="3">
         <v>10086292</v>
@@ -2097,10 +5195,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D22" s="3">
         <v>6864602</v>
@@ -2141,10 +5239,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D23" s="3">
         <v>3673917</v>
@@ -2185,10 +5283,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D24" s="3">
         <v>2966889</v>
@@ -2229,10 +5327,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D25" s="3">
         <v>2721756</v>
@@ -2273,10 +5371,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D26" s="3">
         <v>1978502</v>
@@ -2317,10 +5415,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D27" s="3">
         <v>1458545</v>
@@ -2361,10 +5459,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D28" s="3">
         <v>1383727</v>
@@ -2405,10 +5503,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D29" s="3">
         <v>1247953</v>
@@ -2449,10 +5547,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="D30" s="3">
         <v>1097206</v>
@@ -2493,10 +5591,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="3">
         <v>1055450</v>
@@ -2537,10 +5635,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="D32" s="3">
         <v>610577</v>
@@ -2581,10 +5679,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="D33" s="3">
         <v>380581</v>
@@ -2625,10 +5723,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D34" s="3">
         <v>343709</v>
@@ -2669,10 +5767,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D35" s="3">
         <v>243247</v>
@@ -2713,10 +5811,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D36" s="3">
         <v>64473</v>
@@ -2750,6 +5848,1716 @@
       </c>
       <c r="N36" s="4">
         <v>6.2E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F431FBD6-011F-415B-9936-0AA40F6E0697}">
+  <dimension ref="A2:X9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="H2" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="L2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <f>MAX(population!E2:E36)</f>
+        <v>16.5</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="E3" s="8">
+        <f>MAX(population!H2:H36)</f>
+        <v>1084</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="H3" s="8">
+        <f>MAX(population!I2:I36)</f>
+        <v>94</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="L3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="6" t="str" cm="1">
+        <f t="array" ref="M3:X3">_xlfn.XLOOKUP(L3,population!B2:B36,population!C2:N36,"not found",0)</f>
+        <v>Lucknow</v>
+      </c>
+      <c r="N3" s="6">
+        <v>199812341</v>
+      </c>
+      <c r="O3" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="P3" s="6">
+        <v>104480510</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>95331831</v>
+      </c>
+      <c r="R3" s="6">
+        <v>912</v>
+      </c>
+      <c r="S3" s="6">
+        <v>67.680000000000007</v>
+      </c>
+      <c r="T3" s="6">
+        <v>155111022</v>
+      </c>
+      <c r="U3" s="6">
+        <v>44470455</v>
+      </c>
+      <c r="V3" s="6">
+        <v>240928</v>
+      </c>
+      <c r="W3" s="6">
+        <v>828</v>
+      </c>
+      <c r="X3" s="6">
+        <v>0.20100000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="L4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="6" t="str" cm="1">
+        <f t="array" ref="M4:X4">_xlfn.XLOOKUP(L4,population!B3:B37,population!C3:N37,"not found",0)</f>
+        <v>Jaipur</v>
+      </c>
+      <c r="N4" s="6">
+        <v>68548437</v>
+      </c>
+      <c r="O4" s="6">
+        <v>5.66</v>
+      </c>
+      <c r="P4" s="6">
+        <v>35550997</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>32997440</v>
+      </c>
+      <c r="R4" s="6">
+        <v>928</v>
+      </c>
+      <c r="S4" s="6">
+        <v>66.11</v>
+      </c>
+      <c r="T4" s="6">
+        <v>51540236</v>
+      </c>
+      <c r="U4" s="6">
+        <v>17080776</v>
+      </c>
+      <c r="V4" s="6">
+        <v>342239</v>
+      </c>
+      <c r="W4" s="6">
+        <v>201</v>
+      </c>
+      <c r="X4" s="6">
+        <v>0.214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="E5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="H5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="L5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="6" t="str" cm="1">
+        <f t="array" ref="M5:X5">_xlfn.XLOOKUP(L5,population!B4:B38,population!C4:N38,"not found",0)</f>
+        <v>Shillong</v>
+      </c>
+      <c r="N5" s="6">
+        <v>2966889</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="P5" s="6">
+        <v>1491832</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>1475057</v>
+      </c>
+      <c r="R5" s="6">
+        <v>989</v>
+      </c>
+      <c r="S5" s="6">
+        <v>74.430000000000007</v>
+      </c>
+      <c r="T5" s="6">
+        <v>2368971</v>
+      </c>
+      <c r="U5" s="6">
+        <v>595036</v>
+      </c>
+      <c r="V5" s="6">
+        <v>22429</v>
+      </c>
+      <c r="W5" s="6">
+        <v>132</v>
+      </c>
+      <c r="X5" s="6">
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <f>MIN(population!E2:E36)</f>
+        <v>0.01</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="E6" s="8">
+        <f>MIN(population!H2:H36)</f>
+        <v>618</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="H6" s="8">
+        <f>MIN(population!I2:I36)</f>
+        <v>61.8</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="L6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="6" t="str" cm="1">
+        <f t="array" ref="M6:X6">_xlfn.XLOOKUP(L6,population!B5:B39,population!C5:N39,"not found",0)</f>
+        <v>Gangtok</v>
+      </c>
+      <c r="N6" s="6">
+        <v>610577</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="P6" s="6">
+        <v>323070</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>287507</v>
+      </c>
+      <c r="R6" s="6">
+        <v>890</v>
+      </c>
+      <c r="S6" s="6">
+        <v>81.42</v>
+      </c>
+      <c r="T6" s="6">
+        <v>455962</v>
+      </c>
+      <c r="U6" s="6">
+        <v>151726</v>
+      </c>
+      <c r="V6" s="6">
+        <v>7096</v>
+      </c>
+      <c r="W6" s="6">
+        <v>86</v>
+      </c>
+      <c r="X6" s="6">
+        <v>0.124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="L7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="6" t="str" cm="1">
+        <f t="array" ref="M7:X7">_xlfn.XLOOKUP(L7,population!B6:B40,population!C6:N40,"not found",0)</f>
+        <v>Kavaratti</v>
+      </c>
+      <c r="N7" s="6">
+        <v>64473</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="P7" s="6">
+        <v>33123</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>31350</v>
+      </c>
+      <c r="R7" s="6">
+        <v>946</v>
+      </c>
+      <c r="S7" s="6">
+        <v>91.85</v>
+      </c>
+      <c r="T7" s="6">
+        <v>14121</v>
+      </c>
+      <c r="U7" s="6">
+        <v>50308</v>
+      </c>
+      <c r="V7" s="6">
+        <v>32</v>
+      </c>
+      <c r="W7" s="6">
+        <v>2013</v>
+      </c>
+      <c r="X7" s="6">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="H8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="L8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="6" t="str" cm="1">
+        <f t="array" ref="M8:X8">_xlfn.XLOOKUP(L8,population!B7:B41,population!C7:N41,"not found",0)</f>
+        <v>Itanagar</v>
+      </c>
+      <c r="N8" s="6">
+        <v>1383727</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="P8" s="6">
+        <v>713912</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>669815</v>
+      </c>
+      <c r="R8" s="6">
+        <v>938</v>
+      </c>
+      <c r="S8" s="6">
+        <v>65.38</v>
+      </c>
+      <c r="T8" s="6">
+        <v>1069165</v>
+      </c>
+      <c r="U8" s="6">
+        <v>313446</v>
+      </c>
+      <c r="V8" s="6">
+        <v>83743</v>
+      </c>
+      <c r="W8" s="6">
+        <v>17</v>
+      </c>
+      <c r="X8" s="6">
+        <v>0.25900000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <f>AVERAGE(population!E2:E36)</f>
+        <v>2.8568571428571428</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="E9" s="8">
+        <f>AVERAGE(population!H2:H36)</f>
+        <v>931.2285714285714</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="H9" s="8">
+        <f>AVERAGE(population!I11)</f>
+        <v>78.03</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="L9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="6" t="str" cm="1">
+        <f t="array" ref="M9:X9">_xlfn.XLOOKUP(L9,population!B8:'population'!B42,population!C8:N42,"not found",0)</f>
+        <v>Aizawl</v>
+      </c>
+      <c r="N9" s="6">
+        <v>1097206</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="P9" s="6">
+        <v>555339</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>541867</v>
+      </c>
+      <c r="R9" s="6">
+        <v>976</v>
+      </c>
+      <c r="S9" s="6">
+        <v>91.33</v>
+      </c>
+      <c r="T9" s="6">
+        <v>529037</v>
+      </c>
+      <c r="U9" s="6">
+        <v>561997</v>
+      </c>
+      <c r="V9" s="6">
+        <v>21081</v>
+      </c>
+      <c r="W9" s="6">
+        <v>52</v>
+      </c>
+      <c r="X9" s="6">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881F210B-A9CA-4D54-9D0F-4913621E3B09}">
+  <dimension ref="A3:M76"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="7" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="12">
+        <v>244411</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="13">
+        <v>177710</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="13">
+        <v>960981</v>
+      </c>
+      <c r="J6" s="13">
+        <v>2710051</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="12">
+        <v>183024</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="13">
+        <v>42138631</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="13">
+        <v>561997</v>
+      </c>
+      <c r="J7" s="13">
+        <v>529037</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="12">
+        <v>17445506</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="13">
+        <v>669815</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="13">
+        <v>23578175</v>
+      </c>
+      <c r="J8" s="13">
+        <v>37552529</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="12">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="12">
+        <v>14121</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="13">
+        <v>15266133</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="13">
+        <v>20059666</v>
+      </c>
+      <c r="J9" s="13">
+        <v>52537899</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="12">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="12">
+        <v>17316800</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="13">
+        <v>49821295</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="13">
+        <v>6996124</v>
+      </c>
+      <c r="J10" s="13">
+        <v>34951234</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="12">
+        <v>7025583</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="13">
+        <v>474787</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="13">
+        <v>20234706</v>
+      </c>
+      <c r="J11" s="13">
+        <v>33877297</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="12">
+        <v>42229445</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="13">
+        <v>12712303</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="13">
+        <v>34949729</v>
+      </c>
+      <c r="J12" s="13">
+        <v>37189229</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="12">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="13">
+        <v>149949</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="13">
+        <v>182580</v>
+      </c>
+      <c r="J13" s="13">
+        <v>60331</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="12">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E14" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="13">
+        <v>92946</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="13">
+        <v>3091169</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7025583</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="12">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E15" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="13">
+        <v>7800615</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="13">
+        <v>12905780</v>
+      </c>
+      <c r="J15" s="13">
+        <v>944727</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M15" s="12">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="13">
+        <v>719405</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="13">
+        <v>4388756</v>
+      </c>
+      <c r="J16" s="13">
+        <v>26780526</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="13">
+        <v>28948432</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="13">
+        <v>25712811</v>
+      </c>
+      <c r="J17" s="13">
+        <v>34670817</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="18" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E18" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="13">
+        <v>11856728</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="13">
+        <v>151726</v>
+      </c>
+      <c r="J18" s="13">
+        <v>455962</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="12">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="19" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="13">
+        <v>3382729</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="13">
+        <v>28219075</v>
+      </c>
+      <c r="J19" s="13">
+        <v>56361702</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="12">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="13">
+        <v>5900640</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="13">
+        <v>822132</v>
+      </c>
+      <c r="J20" s="13">
+        <v>1899624</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="12">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E21" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="13">
+        <v>16057819</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="13">
+        <v>313446</v>
+      </c>
+      <c r="J21" s="13">
+        <v>1069165</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" s="12">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="13">
+        <v>30128640</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="13">
+        <v>17080776</v>
+      </c>
+      <c r="J22" s="13">
+        <v>51540236</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22" s="12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="13">
+        <v>17378649</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="13">
+        <v>3414106</v>
+      </c>
+      <c r="J23" s="13">
+        <v>9134820</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23" s="12">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="13">
+        <v>31350</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="13">
+        <v>50308</v>
+      </c>
+      <c r="J24" s="13">
+        <v>14121</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" s="12">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="25" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="13">
+        <v>35014503</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="13">
+        <v>573741</v>
+      </c>
+      <c r="J25" s="13">
+        <v>1406861</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="12">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E26" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="13">
+        <v>54131277</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="13">
+        <v>29134060</v>
+      </c>
+      <c r="J26" s="13">
+        <v>62213676</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="12">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="13">
+        <v>1280219</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="13">
+        <v>44470455</v>
+      </c>
+      <c r="J27" s="13">
+        <v>155111022</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="12">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E28" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1475057</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="13">
+        <v>50827531</v>
+      </c>
+      <c r="J28" s="13">
+        <v>61545441</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" s="12">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E29" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="13">
+        <v>541867</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I29" s="13">
+        <v>906309</v>
+      </c>
+      <c r="J29" s="13">
+        <v>551414</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="12">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="13">
+        <v>953853</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="13">
+        <v>11729609</v>
+      </c>
+      <c r="J30" s="13">
+        <v>92075028</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M30" s="12">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E31" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="13">
+        <v>20762082</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="13">
+        <v>850123</v>
+      </c>
+      <c r="J31" s="13">
+        <v>394341</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M31" s="12">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="32" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E32" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="13">
+        <v>635442</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" s="13">
+        <v>135533</v>
+      </c>
+      <c r="J32" s="13">
+        <v>244411</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="12">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="33" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E33" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="13">
+        <v>13103873</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="13">
+        <v>5936538</v>
+      </c>
+      <c r="J33" s="13">
+        <v>19603658</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M33" s="12">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E34" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="13">
+        <v>32997440</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="13">
+        <v>7929292</v>
+      </c>
+      <c r="J34" s="13">
+        <v>25036946</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M34" s="12">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="35" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E35" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="13">
+        <v>287507</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="13">
+        <v>595036</v>
+      </c>
+      <c r="J35" s="13">
+        <v>2368971</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" s="12">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="36" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E36" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="13">
+        <v>36009055</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="13">
+        <v>688704</v>
+      </c>
+      <c r="J36" s="13">
+        <v>6167805</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M36" s="12">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="37" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="13">
+        <v>1799541</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37" s="13">
+        <v>159829</v>
+      </c>
+      <c r="J37" s="13">
+        <v>183024</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M37" s="12">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="38" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E38" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="13">
+        <v>95331831</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="13">
+        <v>15932171</v>
+      </c>
+      <c r="J38" s="13">
+        <v>17445506</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="12">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="39" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E39" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="13">
+        <v>4948519</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I39" s="13">
+        <v>373542974</v>
+      </c>
+      <c r="J39" s="13">
+        <v>833652994</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" s="12">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="40" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E40" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="13">
+        <v>44467088</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40" s="12">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="41" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E41" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" s="13">
+        <v>587447730</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M41" s="12">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="42" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L42" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="M42" s="12">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L43" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M43" s="12">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L44" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L45" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M45" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M46" s="12">
+        <v>9.2799999999999994</v>
+      </c>
+    </row>
+    <row r="47" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L47" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="M47" s="12">
+        <v>9.2799999999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L48" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M48" s="12">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L49" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="12">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L50" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L51" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M51" s="12">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L52" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M52" s="12">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L53" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M53" s="12">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L54" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="12">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L55" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M55" s="12">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L56" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M56" s="12">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="57" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L57" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="M57" s="12">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="58" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L58" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M58" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="59" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L59" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L60" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M60" s="12">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="61" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L61" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M61" s="12">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="62" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L62" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M62" s="12">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L63" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="12">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L64" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M64" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M65" s="12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L66" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" s="12">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L67" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="12">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L68" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M68" s="12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L69" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M69" s="12">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="M70" s="12">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L71" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M71" s="12">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L72" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M72" s="12">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L73" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M73" s="12">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L74" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M74" s="12">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L75" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="12">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L76" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="M76" s="12">
+        <v>99.99</v>
       </c>
     </row>
   </sheetData>

--- a/population.csv.xlsx
+++ b/population.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Project\Indian Population Data Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BD8FB3-6457-447E-BB0F-5D7F160F7A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B4099-5B02-420F-93F1-66877240B4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB82829B-6F12-444B-8421-B58D62F0B729}"/>
   </bookViews>
@@ -19,8 +19,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
-    <pivotCache cacheId="22" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -871,7 +871,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -880,20 +880,19 @@
     <xf numFmtId="9" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2723,7 +2722,191 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F7B912B-B7BC-4364-BBA6-38B4B0148DFC}" name="PivotTable4" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3E7D3-975D-432E-ACA4-EC6B906FDDBE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="37">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="35">
+        <item x="31"/>
+        <item x="30"/>
+        <item x="27"/>
+        <item x="17"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="14"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="32"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="25"/>
+        <item x="11"/>
+        <item x="33"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="37">
+        <item h="1" x="2"/>
+        <item h="1" x="26"/>
+        <item h="1" x="7"/>
+        <item h="1" x="12"/>
+        <item h="1" x="4"/>
+        <item h="1" x="18"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="15"/>
+        <item h="1" x="13"/>
+        <item h="1" x="10"/>
+        <item h="1" x="22"/>
+        <item h="1" x="8"/>
+        <item h="1" x="16"/>
+        <item x="14"/>
+        <item x="32"/>
+        <item h="1" x="3"/>
+        <item h="1" x="9"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item x="19"/>
+        <item h="1" x="6"/>
+        <item h="1" x="30"/>
+        <item h="1" x="1"/>
+        <item h="1" x="20"/>
+        <item h="1" x="27"/>
+        <item h="1" x="29"/>
+        <item h="1" x="17"/>
+        <item x="31"/>
+        <item h="1" x="33"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="28"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item h="1" x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F7B912B-B7BC-4364-BBA6-38B4B0148DFC}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="L5:M76" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -3133,8 +3316,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{51E9E64C-34E6-49FF-ABC4-DCBA46C9B4F0}" name="PivotTable3" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{51E9E64C-34E6-49FF-ABC4-DCBA46C9B4F0}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H5:J39" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -3402,8 +3585,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283C2D54-EA66-46DD-A52C-DBEC61E2F94E}" name="PivotTable2" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283C2D54-EA66-46DD-A52C-DBEC61E2F94E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0">
@@ -3733,190 +3916,6 @@
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Females" fld="6" baseField="0" baseItem="0" numFmtId="3"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3E7D3-975D-432E-ACA4-EC6B906FDDBE}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="37">
-        <item x="31"/>
-        <item x="4"/>
-        <item x="26"/>
-        <item x="13"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="17"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item x="20"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="34"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="6"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="35"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="35">
-        <item x="31"/>
-        <item x="30"/>
-        <item x="27"/>
-        <item x="17"/>
-        <item x="29"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="28"/>
-        <item x="14"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="32"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="22"/>
-        <item x="15"/>
-        <item x="23"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="25"/>
-        <item x="11"/>
-        <item x="33"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="37">
-        <item h="1" x="2"/>
-        <item h="1" x="26"/>
-        <item h="1" x="7"/>
-        <item h="1" x="12"/>
-        <item h="1" x="4"/>
-        <item h="1" x="18"/>
-        <item h="1" x="0"/>
-        <item h="1" x="5"/>
-        <item h="1" x="15"/>
-        <item h="1" x="13"/>
-        <item h="1" x="10"/>
-        <item h="1" x="22"/>
-        <item h="1" x="8"/>
-        <item h="1" x="16"/>
-        <item x="14"/>
-        <item x="32"/>
-        <item h="1" x="3"/>
-        <item h="1" x="9"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item x="19"/>
-        <item h="1" x="6"/>
-        <item h="1" x="30"/>
-        <item h="1" x="1"/>
-        <item h="1" x="20"/>
-        <item h="1" x="27"/>
-        <item h="1" x="29"/>
-        <item h="1" x="17"/>
-        <item x="31"/>
-        <item h="1" x="33"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item h="1" x="28"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item h="1" x="35"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -4250,20 +4249,20 @@
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5876,19 +5875,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="E2" s="9" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="H2" s="9" t="s">
+      <c r="F2" s="12"/>
+      <c r="H2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="9"/>
+      <c r="I2" s="12"/>
       <c r="L2" s="7" t="s">
         <v>1</v>
       </c>
@@ -5930,22 +5929,22 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <f>MAX(population!E2:E36)</f>
         <v>16.5</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="E3" s="8">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="E3" s="13">
         <f>MAX(population!H2:H36)</f>
         <v>1084</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="H3" s="8">
+      <c r="F3" s="13"/>
+      <c r="H3" s="13">
         <f>MAX(population!I2:I36)</f>
         <v>94</v>
       </c>
-      <c r="I3" s="8"/>
+      <c r="I3" s="13"/>
       <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
@@ -6030,19 +6029,19 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="E5" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="F5" s="12"/>
+      <c r="H5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="9"/>
+      <c r="I5" s="12"/>
       <c r="L5" s="6" t="s">
         <v>54</v>
       </c>
@@ -6085,22 +6084,22 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="13">
         <f>MIN(population!E2:E36)</f>
         <v>0.01</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="E6" s="8">
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="E6" s="13">
         <f>MIN(population!H2:H36)</f>
         <v>618</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="H6" s="8">
+      <c r="F6" s="13"/>
+      <c r="H6" s="13">
         <f>MIN(population!I2:I36)</f>
         <v>61.8</v>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="13"/>
       <c r="L6" s="6" t="s">
         <v>68</v>
       </c>
@@ -6185,19 +6184,19 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="E8" s="9" t="s">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="E8" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="H8" s="9" t="s">
+      <c r="F8" s="12"/>
+      <c r="H8" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="9"/>
+      <c r="I8" s="12"/>
       <c r="L8" s="6" t="s">
         <v>62</v>
       </c>
@@ -6240,22 +6239,22 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="13">
         <f>AVERAGE(population!E2:E36)</f>
         <v>2.8568571428571428</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="E9" s="8">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="E9" s="13">
         <f>AVERAGE(population!H2:H36)</f>
         <v>931.2285714285714</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="H9" s="8">
+      <c r="F9" s="13"/>
+      <c r="H9" s="13">
         <f>AVERAGE(population!I11)</f>
         <v>78.03</v>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="13"/>
       <c r="L9" s="6" t="s">
         <v>66</v>
       </c>
@@ -6299,11 +6298,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
@@ -6311,12 +6311,11 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H8:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6374,25 +6373,25 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>78</v>
       </c>
       <c r="F3" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="I3" t="s">
         <v>91</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M3" t="s">
@@ -6400,19 +6399,19 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>88</v>
       </c>
       <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>88</v>
       </c>
       <c r="F5" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>88</v>
       </c>
       <c r="I5" t="s">
@@ -6421,7 +6420,7 @@
       <c r="J5" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M5" t="s">
@@ -6429,1134 +6428,1134 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6">
         <v>244411</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="10">
         <v>177710</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="10">
         <v>960981</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="10">
         <v>2710051</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6">
         <v>0.03</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7">
         <v>183024</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="10">
         <v>42138631</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="10">
         <v>561997</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="10">
         <v>529037</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7">
         <v>0.03</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8">
         <v>17445506</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>669815</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>23578175</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="10">
         <v>37552529</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8">
         <v>6.99</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9">
         <v>14121</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="10">
         <v>15266133</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>20059666</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="10">
         <v>52537899</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9">
         <v>6.99</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10">
         <v>17316800</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>49821295</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>6996124</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="10">
         <v>34951234</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10">
         <v>0.11</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11">
         <v>7025583</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>474787</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="10">
         <v>20234706</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="10">
         <v>33877297</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11">
         <v>0.11</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12">
         <v>42229445</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>12712303</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>34949729</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="10">
         <v>37189229</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12">
         <v>2.58</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="10">
         <v>149949</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>182580</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="10">
         <v>60331</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13">
         <v>2.58</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="10">
         <v>92946</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>3091169</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="10">
         <v>7025583</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14">
         <v>8.6</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="10">
         <v>7800615</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>12905780</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="10">
         <v>944727</v>
       </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15">
         <v>8.6</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="10">
         <v>719405</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>4388756</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="10">
         <v>26780526</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16">
         <v>0.09</v>
       </c>
     </row>
     <row r="17" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="10">
         <v>28948432</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <v>25712811</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="10">
         <v>34670817</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17">
         <v>0.09</v>
       </c>
     </row>
     <row r="18" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="10">
         <v>11856728</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="10">
         <v>151726</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="10">
         <v>455962</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18">
         <v>2.11</v>
       </c>
     </row>
     <row r="19" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="10">
         <v>3382729</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="10">
         <v>28219075</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="10">
         <v>56361702</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19">
         <v>2.11</v>
       </c>
     </row>
     <row r="20" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="10">
         <v>5900640</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="10">
         <v>822132</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="10">
         <v>1899624</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20">
         <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="10">
         <v>16057819</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="10">
         <v>313446</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="10">
         <v>1069165</v>
       </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="10">
         <v>30128640</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="10">
         <v>17080776</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="10">
         <v>51540236</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22">
         <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="10">
         <v>17378649</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="10">
         <v>3414106</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="10">
         <v>9134820</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23">
         <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="10">
         <v>31350</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="10">
         <v>50308</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="10">
         <v>14121</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="12">
+      <c r="M24">
         <v>1.39</v>
       </c>
     </row>
     <row r="25" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="10">
         <v>35014503</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="H25" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="10">
         <v>573741</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="10">
         <v>1406861</v>
       </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="M25" s="12">
+      <c r="M25">
         <v>1.39</v>
       </c>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="10">
         <v>54131277</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="10">
         <v>29134060</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="10">
         <v>62213676</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="12">
+      <c r="M26">
         <v>0.12</v>
       </c>
     </row>
     <row r="27" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="10">
         <v>1280219</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="10">
         <v>44470455</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="10">
         <v>155111022</v>
       </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="M27" s="12">
+      <c r="M27">
         <v>0.12</v>
       </c>
     </row>
     <row r="28" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="10">
         <v>1475057</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="10">
         <v>50827531</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="10">
         <v>61545441</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M28" s="12">
+      <c r="M28">
         <v>4.99</v>
       </c>
     </row>
     <row r="29" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="10">
         <v>541867</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="10">
         <v>906309</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="10">
         <v>551414</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="L29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M29" s="12">
+      <c r="M29">
         <v>4.99</v>
       </c>
     </row>
     <row r="30" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="10">
         <v>953853</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="10">
         <v>11729609</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="10">
         <v>92075028</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M30">
         <v>2.09</v>
       </c>
     </row>
     <row r="31" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="10">
         <v>20762082</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="H31" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="10">
         <v>850123</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="10">
         <v>394341</v>
       </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M31" s="12">
+      <c r="M31">
         <v>2.09</v>
       </c>
     </row>
     <row r="32" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="10">
         <v>635442</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="10">
         <v>135533</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J32" s="10">
         <v>244411</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M32" s="12">
+      <c r="M32">
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="33" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="10">
         <v>13103873</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H33" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="10">
         <v>5936538</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="10">
         <v>19603658</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M33" s="12">
+      <c r="M33">
         <v>0.56999999999999995</v>
       </c>
     </row>
     <row r="34" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="10">
         <v>32997440</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="10">
         <v>7929292</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="10">
         <v>25036946</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M34">
         <v>1.04</v>
       </c>
     </row>
     <row r="35" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="10">
         <v>287507</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="10">
         <v>595036</v>
       </c>
-      <c r="J35" s="13">
+      <c r="J35" s="10">
         <v>2368971</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L35" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M35" s="12">
+      <c r="M35">
         <v>1.04</v>
       </c>
     </row>
     <row r="36" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="10">
         <v>36009055</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="10">
         <v>688704</v>
       </c>
-      <c r="J36" s="13">
+      <c r="J36" s="10">
         <v>6167805</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M36" s="12">
+      <c r="M36">
         <v>2.72</v>
       </c>
     </row>
     <row r="37" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="10">
         <v>1799541</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="10">
         <v>159829</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="10">
         <v>183024</v>
       </c>
-      <c r="L37" s="14" t="s">
+      <c r="L37" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="12">
+      <c r="M37">
         <v>2.72</v>
       </c>
     </row>
     <row r="38" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="10">
         <v>95331831</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="10">
         <v>15932171</v>
       </c>
-      <c r="J38" s="13">
+      <c r="J38" s="10">
         <v>17445506</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38">
         <v>5.05</v>
       </c>
     </row>
     <row r="39" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="10">
         <v>4948519</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="10">
         <v>373542974</v>
       </c>
-      <c r="J39" s="13">
+      <c r="J39" s="10">
         <v>833652994</v>
       </c>
-      <c r="L39" s="14" t="s">
+      <c r="L39" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M39" s="12">
+      <c r="M39">
         <v>5.05</v>
       </c>
     </row>
     <row r="40" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="10">
         <v>44467088</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M40" s="12">
+      <c r="M40">
         <v>2.76</v>
       </c>
     </row>
     <row r="41" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="10">
         <v>587447730</v>
       </c>
-      <c r="L41" s="14" t="s">
+      <c r="L41" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="M41" s="12">
+      <c r="M41">
         <v>2.76</v>
       </c>
     </row>
     <row r="42" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M42">
         <v>0.01</v>
       </c>
     </row>
     <row r="43" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L43" s="14" t="s">
+      <c r="L43" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M43" s="12">
+      <c r="M43">
         <v>0.01</v>
       </c>
     </row>
     <row r="44" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M44" s="12">
+      <c r="M44">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L45" s="14" t="s">
+      <c r="L45" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="12">
+      <c r="M45">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M46" s="12">
+      <c r="M46">
         <v>9.2799999999999994</v>
       </c>
     </row>
     <row r="47" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L47" s="14" t="s">
+      <c r="L47" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="12">
+      <c r="M47">
         <v>9.2799999999999994</v>
       </c>
     </row>
     <row r="48" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="M48" s="12">
+      <c r="M48">
         <v>0.21</v>
       </c>
     </row>
     <row r="49" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L49" s="14" t="s">
+      <c r="L49" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M49" s="12">
+      <c r="M49">
         <v>0.21</v>
       </c>
     </row>
     <row r="50" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M50" s="12">
+      <c r="M50">
         <v>0.25</v>
       </c>
     </row>
     <row r="51" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L51" s="14" t="s">
+      <c r="L51" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="M51" s="12">
+      <c r="M51">
         <v>0.25</v>
       </c>
     </row>
     <row r="52" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M52" s="12">
+      <c r="M52">
         <v>0.09</v>
       </c>
     </row>
     <row r="53" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L53" s="14" t="s">
+      <c r="L53" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M53" s="12">
+      <c r="M53">
         <v>0.09</v>
       </c>
     </row>
     <row r="54" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L54" s="11" t="s">
+      <c r="L54" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M54" s="12">
+      <c r="M54">
         <v>0.16</v>
       </c>
     </row>
     <row r="55" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L55" s="14" t="s">
+      <c r="L55" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M55" s="12">
+      <c r="M55">
         <v>0.16</v>
       </c>
     </row>
     <row r="56" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="12">
+      <c r="M56">
         <v>3.47</v>
       </c>
     </row>
     <row r="57" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L57" s="14" t="s">
+      <c r="L57" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M57" s="12">
+      <c r="M57">
         <v>3.47</v>
       </c>
     </row>
     <row r="58" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M58" s="12">
+      <c r="M58">
         <v>0.1</v>
       </c>
     </row>
     <row r="59" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L59" s="14" t="s">
+      <c r="L59" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="M59" s="12">
+      <c r="M59">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M60" s="12">
+      <c r="M60">
         <v>2.29</v>
       </c>
     </row>
     <row r="61" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L61" s="14" t="s">
+      <c r="L61" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M61" s="12">
+      <c r="M61">
         <v>2.29</v>
       </c>
     </row>
     <row r="62" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M62" s="12">
+      <c r="M62">
         <v>5.66</v>
       </c>
     </row>
     <row r="63" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L63" s="14" t="s">
+      <c r="L63" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M63" s="12">
+      <c r="M63">
         <v>5.66</v>
       </c>
     </row>
     <row r="64" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M64" s="12">
+      <c r="M64">
         <v>0.05</v>
       </c>
     </row>
     <row r="65" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L65" s="14" t="s">
+      <c r="L65" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="M65" s="12">
+      <c r="M65">
         <v>0.05</v>
       </c>
     </row>
     <row r="66" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M66" s="12">
+      <c r="M66">
         <v>5.96</v>
       </c>
     </row>
     <row r="67" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L67" s="14" t="s">
+      <c r="L67" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M67" s="12">
+      <c r="M67">
         <v>5.96</v>
       </c>
     </row>
     <row r="68" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M68" s="12">
+      <c r="M68">
         <v>0.3</v>
       </c>
     </row>
     <row r="69" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L69" s="14" t="s">
+      <c r="L69" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M69" s="12">
+      <c r="M69">
         <v>0.3</v>
       </c>
     </row>
     <row r="70" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M70" s="12">
+      <c r="M70">
         <v>16.5</v>
       </c>
     </row>
     <row r="71" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L71" s="14" t="s">
+      <c r="L71" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M71" s="12">
+      <c r="M71">
         <v>16.5</v>
       </c>
     </row>
     <row r="72" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M72" s="12">
+      <c r="M72">
         <v>0.83</v>
       </c>
     </row>
     <row r="73" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L73" s="14" t="s">
+      <c r="L73" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M73" s="12">
+      <c r="M73">
         <v>0.83</v>
       </c>
     </row>
     <row r="74" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M74" s="12">
+      <c r="M74">
         <v>7.54</v>
       </c>
     </row>
     <row r="75" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L75" s="14" t="s">
+      <c r="L75" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="M75" s="12">
+      <c r="M75">
         <v>7.54</v>
       </c>
     </row>
     <row r="76" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="M76" s="12">
+      <c r="M76">
         <v>99.99</v>
       </c>
     </row>

--- a/population.csv.xlsx
+++ b/population.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Project\Indian Population Data Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8B4099-5B02-420F-93F1-66877240B4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ED63F8-AA14-4807-BE25-B77AE7D423CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB82829B-6F12-444B-8421-B58D62F0B729}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FB82829B-6F12-444B-8421-B58D62F0B729}"/>
   </bookViews>
   <sheets>
     <sheet name="population" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="97">
   <si>
     <t>Rank</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Sum of Urban Population</t>
+  </si>
+  <si>
+    <t>Sum of Males</t>
   </si>
 </sst>
 </file>
@@ -888,10 +891,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1283,43 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Males" numFmtId="3">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="33123" maxValue="104480510"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="33123" maxValue="104480510" count="35">
+        <n v="104480510"/>
+        <n v="58243056"/>
+        <n v="54278157"/>
+        <n v="46809027"/>
+        <n v="42442146"/>
+        <n v="37612306"/>
+        <n v="36137975"/>
+        <n v="35550997"/>
+        <n v="30966657"/>
+        <n v="31491260"/>
+        <n v="21212136"/>
+        <n v="16027412"/>
+        <n v="16930315"/>
+        <n v="15939443"/>
+        <n v="14639465"/>
+        <n v="12832895"/>
+        <n v="13494734"/>
+        <n v="8887326"/>
+        <n v="6640662"/>
+        <n v="5137773"/>
+        <n v="3481873"/>
+        <n v="1874376"/>
+        <n v="1491832"/>
+        <n v="1290171"/>
+        <n v="1024649"/>
+        <n v="739140"/>
+        <n v="713912"/>
+        <n v="612511"/>
+        <n v="555339"/>
+        <n v="580663"/>
+        <n v="323070"/>
+        <n v="202871"/>
+        <n v="193760"/>
+        <n v="150301"/>
+        <n v="33123"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Females" numFmtId="3">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="31350" maxValue="95331831"/>
@@ -2164,7 +2203,7 @@
     <x v="0"/>
     <n v="199812341"/>
     <x v="0"/>
-    <n v="104480510"/>
+    <x v="0"/>
     <n v="95331831"/>
     <x v="0"/>
     <x v="0"/>
@@ -2180,7 +2219,7 @@
     <x v="1"/>
     <n v="112374333"/>
     <x v="1"/>
-    <n v="58243056"/>
+    <x v="1"/>
     <n v="54131277"/>
     <x v="1"/>
     <x v="1"/>
@@ -2196,7 +2235,7 @@
     <x v="2"/>
     <n v="104099452"/>
     <x v="2"/>
-    <n v="54278157"/>
+    <x v="2"/>
     <n v="49821295"/>
     <x v="2"/>
     <x v="2"/>
@@ -2212,7 +2251,7 @@
     <x v="3"/>
     <n v="91276115"/>
     <x v="3"/>
-    <n v="46809027"/>
+    <x v="3"/>
     <n v="44467088"/>
     <x v="3"/>
     <x v="3"/>
@@ -2228,7 +2267,7 @@
     <x v="4"/>
     <n v="84580777"/>
     <x v="4"/>
-    <n v="42442146"/>
+    <x v="4"/>
     <n v="42138631"/>
     <x v="4"/>
     <x v="4"/>
@@ -2244,7 +2283,7 @@
     <x v="5"/>
     <n v="72626809"/>
     <x v="5"/>
-    <n v="37612306"/>
+    <x v="5"/>
     <n v="35014503"/>
     <x v="5"/>
     <x v="5"/>
@@ -2260,7 +2299,7 @@
     <x v="6"/>
     <n v="72147030"/>
     <x v="6"/>
-    <n v="36137975"/>
+    <x v="6"/>
     <n v="36009055"/>
     <x v="6"/>
     <x v="6"/>
@@ -2276,7 +2315,7 @@
     <x v="7"/>
     <n v="68548437"/>
     <x v="7"/>
-    <n v="35550997"/>
+    <x v="7"/>
     <n v="32997440"/>
     <x v="7"/>
     <x v="7"/>
@@ -2292,7 +2331,7 @@
     <x v="8"/>
     <n v="61095297"/>
     <x v="8"/>
-    <n v="30966657"/>
+    <x v="8"/>
     <n v="30128640"/>
     <x v="8"/>
     <x v="8"/>
@@ -2308,7 +2347,7 @@
     <x v="9"/>
     <n v="60439692"/>
     <x v="9"/>
-    <n v="31491260"/>
+    <x v="9"/>
     <n v="28948432"/>
     <x v="9"/>
     <x v="9"/>
@@ -2324,7 +2363,7 @@
     <x v="10"/>
     <n v="41974218"/>
     <x v="10"/>
-    <n v="21212136"/>
+    <x v="10"/>
     <n v="20762082"/>
     <x v="10"/>
     <x v="10"/>
@@ -2340,7 +2379,7 @@
     <x v="11"/>
     <n v="33406061"/>
     <x v="11"/>
-    <n v="16027412"/>
+    <x v="11"/>
     <n v="17378649"/>
     <x v="11"/>
     <x v="11"/>
@@ -2356,7 +2395,7 @@
     <x v="12"/>
     <n v="32988134"/>
     <x v="12"/>
-    <n v="16930315"/>
+    <x v="12"/>
     <n v="16057819"/>
     <x v="12"/>
     <x v="12"/>
@@ -2372,7 +2411,7 @@
     <x v="13"/>
     <n v="31205576"/>
     <x v="13"/>
-    <n v="15939443"/>
+    <x v="13"/>
     <n v="15266133"/>
     <x v="13"/>
     <x v="13"/>
@@ -2388,7 +2427,7 @@
     <x v="14"/>
     <n v="27743338"/>
     <x v="14"/>
-    <n v="14639465"/>
+    <x v="14"/>
     <n v="13103873"/>
     <x v="14"/>
     <x v="14"/>
@@ -2404,7 +2443,7 @@
     <x v="15"/>
     <n v="25545198"/>
     <x v="15"/>
-    <n v="12832895"/>
+    <x v="15"/>
     <n v="12712303"/>
     <x v="15"/>
     <x v="15"/>
@@ -2420,7 +2459,7 @@
     <x v="14"/>
     <n v="25351462"/>
     <x v="16"/>
-    <n v="13494734"/>
+    <x v="16"/>
     <n v="11856728"/>
     <x v="16"/>
     <x v="16"/>
@@ -2436,7 +2475,7 @@
     <x v="16"/>
     <n v="16787941"/>
     <x v="17"/>
-    <n v="8887326"/>
+    <x v="17"/>
     <n v="7800615"/>
     <x v="17"/>
     <x v="17"/>
@@ -2452,7 +2491,7 @@
     <x v="17"/>
     <n v="12541302"/>
     <x v="18"/>
-    <n v="6640662"/>
+    <x v="18"/>
     <n v="5900640"/>
     <x v="18"/>
     <x v="18"/>
@@ -2468,7 +2507,7 @@
     <x v="18"/>
     <n v="10086292"/>
     <x v="19"/>
-    <n v="5137773"/>
+    <x v="19"/>
     <n v="4948519"/>
     <x v="19"/>
     <x v="19"/>
@@ -2484,7 +2523,7 @@
     <x v="19"/>
     <n v="6864602"/>
     <x v="20"/>
-    <n v="3481873"/>
+    <x v="20"/>
     <n v="3382729"/>
     <x v="20"/>
     <x v="20"/>
@@ -2500,7 +2539,7 @@
     <x v="20"/>
     <n v="3673917"/>
     <x v="21"/>
-    <n v="1874376"/>
+    <x v="21"/>
     <n v="1799541"/>
     <x v="21"/>
     <x v="21"/>
@@ -2516,7 +2555,7 @@
     <x v="21"/>
     <n v="2966889"/>
     <x v="22"/>
-    <n v="1491832"/>
+    <x v="22"/>
     <n v="1475057"/>
     <x v="22"/>
     <x v="22"/>
@@ -2532,7 +2571,7 @@
     <x v="22"/>
     <n v="2721756"/>
     <x v="23"/>
-    <n v="1290171"/>
+    <x v="23"/>
     <n v="1280219"/>
     <x v="23"/>
     <x v="23"/>
@@ -2548,7 +2587,7 @@
     <x v="23"/>
     <n v="1978502"/>
     <x v="24"/>
-    <n v="1024649"/>
+    <x v="24"/>
     <n v="953853"/>
     <x v="5"/>
     <x v="24"/>
@@ -2564,7 +2603,7 @@
     <x v="24"/>
     <n v="1458545"/>
     <x v="25"/>
-    <n v="739140"/>
+    <x v="25"/>
     <n v="719405"/>
     <x v="8"/>
     <x v="25"/>
@@ -2580,7 +2619,7 @@
     <x v="25"/>
     <n v="1383727"/>
     <x v="26"/>
-    <n v="713912"/>
+    <x v="26"/>
     <n v="669815"/>
     <x v="24"/>
     <x v="26"/>
@@ -2596,7 +2635,7 @@
     <x v="26"/>
     <n v="1247953"/>
     <x v="27"/>
-    <n v="612511"/>
+    <x v="27"/>
     <n v="635442"/>
     <x v="25"/>
     <x v="27"/>
@@ -2612,7 +2651,7 @@
     <x v="27"/>
     <n v="1097206"/>
     <x v="28"/>
-    <n v="555339"/>
+    <x v="28"/>
     <n v="541867"/>
     <x v="26"/>
     <x v="28"/>
@@ -2628,7 +2667,7 @@
     <x v="14"/>
     <n v="1055450"/>
     <x v="28"/>
-    <n v="580663"/>
+    <x v="29"/>
     <n v="474787"/>
     <x v="27"/>
     <x v="29"/>
@@ -2644,7 +2683,7 @@
     <x v="28"/>
     <n v="610577"/>
     <x v="29"/>
-    <n v="323070"/>
+    <x v="30"/>
     <n v="287507"/>
     <x v="28"/>
     <x v="30"/>
@@ -2660,7 +2699,7 @@
     <x v="29"/>
     <n v="380581"/>
     <x v="30"/>
-    <n v="202871"/>
+    <x v="31"/>
     <n v="177710"/>
     <x v="29"/>
     <x v="31"/>
@@ -2676,7 +2715,7 @@
     <x v="30"/>
     <n v="343709"/>
     <x v="30"/>
-    <n v="193760"/>
+    <x v="32"/>
     <n v="149949"/>
     <x v="30"/>
     <x v="32"/>
@@ -2692,7 +2731,7 @@
     <x v="31"/>
     <n v="243247"/>
     <x v="31"/>
-    <n v="150301"/>
+    <x v="33"/>
     <n v="92946"/>
     <x v="31"/>
     <x v="33"/>
@@ -2708,7 +2747,7 @@
     <x v="32"/>
     <n v="64473"/>
     <x v="32"/>
-    <n v="33123"/>
+    <x v="34"/>
     <n v="31350"/>
     <x v="32"/>
     <x v="34"/>
@@ -2722,192 +2761,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3E7D3-975D-432E-ACA4-EC6B906FDDBE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="37">
-        <item x="31"/>
-        <item x="4"/>
-        <item x="26"/>
-        <item x="13"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="17"/>
-        <item x="25"/>
-        <item x="9"/>
-        <item x="16"/>
-        <item x="20"/>
-        <item x="18"/>
-        <item x="12"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="34"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="23"/>
-        <item x="22"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="6"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="35"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="35">
-        <item x="31"/>
-        <item x="30"/>
-        <item x="27"/>
-        <item x="17"/>
-        <item x="29"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="28"/>
-        <item x="14"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="24"/>
-        <item x="32"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="13"/>
-        <item x="21"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="26"/>
-        <item x="10"/>
-        <item x="22"/>
-        <item x="15"/>
-        <item x="23"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="25"/>
-        <item x="11"/>
-        <item x="33"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="37">
-        <item h="1" x="2"/>
-        <item h="1" x="26"/>
-        <item h="1" x="7"/>
-        <item h="1" x="12"/>
-        <item h="1" x="4"/>
-        <item h="1" x="18"/>
-        <item h="1" x="0"/>
-        <item h="1" x="5"/>
-        <item h="1" x="15"/>
-        <item h="1" x="13"/>
-        <item h="1" x="10"/>
-        <item h="1" x="22"/>
-        <item h="1" x="8"/>
-        <item h="1" x="16"/>
-        <item x="14"/>
-        <item x="32"/>
-        <item h="1" x="3"/>
-        <item h="1" x="9"/>
-        <item h="1" x="23"/>
-        <item h="1" x="24"/>
-        <item x="19"/>
-        <item h="1" x="6"/>
-        <item h="1" x="30"/>
-        <item h="1" x="1"/>
-        <item h="1" x="20"/>
-        <item h="1" x="27"/>
-        <item h="1" x="29"/>
-        <item h="1" x="17"/>
-        <item x="31"/>
-        <item h="1" x="33"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item h="1" x="28"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item h="1" x="35"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F7B912B-B7BC-4364-BBA6-38B4B0148DFC}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="L5:M76" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F7B912B-B7BC-4364-BBA6-38B4B0148DFC}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="M5:N76" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -3316,9 +3171,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{51E9E64C-34E6-49FF-ABC4-DCBA46C9B4F0}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H5:J39" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{51E9E64C-34E6-49FF-ABC4-DCBA46C9B4F0}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I5:K39" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -3585,9 +3440,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283C2D54-EA66-46DD-A52C-DBEC61E2F94E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{283C2D54-EA66-46DD-A52C-DBEC61E2F94E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:G41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="14">
     <pivotField showAll="0">
       <items count="36">
@@ -3709,9 +3564,48 @@
     </pivotField>
     <pivotField numFmtId="3" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0">
+      <items count="36">
+        <item x="34"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField dataField="1" numFmtId="3" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
       <items count="34">
         <item x="31"/>
         <item x="30"/>
@@ -3789,8 +3683,86 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="3" showAll="0"/>
-    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField axis="axisPage" numFmtId="3" showAll="0">
+      <items count="36">
+        <item x="34"/>
+        <item x="29"/>
+        <item x="33"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="27"/>
+        <item x="30"/>
+        <item x="28"/>
+        <item x="25"/>
+        <item x="17"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" numFmtId="3" showAll="0">
+      <items count="36">
+        <item x="34"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="26"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="22"/>
+        <item x="20"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="25"/>
+        <item x="21"/>
+        <item x="29"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -3908,14 +3880,208 @@
       <x/>
     </i>
   </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="9" hier="-1"/>
+    <pageField fld="10" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Sum of Females" fld="6" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="Sum of Males" fld="5" baseField="0" baseItem="0" numFmtId="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80C3E7D3-975D-432E-ACA4-EC6B906FDDBE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="37">
+        <item x="31"/>
+        <item x="4"/>
+        <item x="26"/>
+        <item x="13"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="17"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="12"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="34"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="21"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="35">
+        <item x="31"/>
+        <item x="30"/>
+        <item x="27"/>
+        <item x="17"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="28"/>
+        <item x="14"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="24"/>
+        <item x="32"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="13"/>
+        <item x="21"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="26"/>
+        <item x="10"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="25"/>
+        <item x="11"/>
+        <item x="33"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="37">
+        <item h="1" x="2"/>
+        <item h="1" x="26"/>
+        <item h="1" x="7"/>
+        <item h="1" x="12"/>
+        <item h="1" x="4"/>
+        <item h="1" x="18"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="15"/>
+        <item h="1" x="13"/>
+        <item h="1" x="10"/>
+        <item h="1" x="22"/>
+        <item h="1" x="8"/>
+        <item h="1" x="16"/>
+        <item x="14"/>
+        <item x="32"/>
+        <item h="1" x="3"/>
+        <item h="1" x="9"/>
+        <item h="1" x="23"/>
+        <item h="1" x="24"/>
+        <item x="19"/>
+        <item h="1" x="6"/>
+        <item h="1" x="30"/>
+        <item h="1" x="1"/>
+        <item h="1" x="20"/>
+        <item h="1" x="27"/>
+        <item h="1" x="29"/>
+        <item h="1" x="17"/>
+        <item x="31"/>
+        <item h="1" x="33"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="28"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item h="1" x="35"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="7" hier="-1"/>
+    <pageField fld="8" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Sum of Females" fld="6" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="Sum of Rural Population" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5875,19 +6041,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="E2" s="12" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="E2" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="H2" s="12" t="s">
+      <c r="F2" s="13"/>
+      <c r="H2" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="12"/>
+      <c r="I2" s="13"/>
       <c r="L2" s="7" t="s">
         <v>1</v>
       </c>
@@ -5929,22 +6095,22 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <f>MAX(population!E2:E36)</f>
         <v>16.5</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="E3" s="13">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="E3" s="12">
         <f>MAX(population!H2:H36)</f>
         <v>1084</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="H3" s="13">
+      <c r="F3" s="12"/>
+      <c r="H3" s="12">
         <f>MAX(population!I2:I36)</f>
         <v>94</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="12"/>
       <c r="L3" s="6" t="s">
         <v>13</v>
       </c>
@@ -6029,19 +6195,19 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="H5" s="12" t="s">
+      <c r="F5" s="13"/>
+      <c r="H5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="12"/>
+      <c r="I5" s="13"/>
       <c r="L5" s="6" t="s">
         <v>54</v>
       </c>
@@ -6084,22 +6250,22 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <f>MIN(population!E2:E36)</f>
         <v>0.01</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="E6" s="13">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="E6" s="12">
         <f>MIN(population!H2:H36)</f>
         <v>618</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="H6" s="13">
+      <c r="F6" s="12"/>
+      <c r="H6" s="12">
         <f>MIN(population!I2:I36)</f>
         <v>61.8</v>
       </c>
-      <c r="I6" s="13"/>
+      <c r="I6" s="12"/>
       <c r="L6" s="6" t="s">
         <v>68</v>
       </c>
@@ -6184,19 +6350,19 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="E8" s="12" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="E8" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="H8" s="12" t="s">
+      <c r="F8" s="13"/>
+      <c r="H8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="12"/>
+      <c r="I8" s="13"/>
       <c r="L8" s="6" t="s">
         <v>62</v>
       </c>
@@ -6239,22 +6405,22 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <f>AVERAGE(population!E2:E36)</f>
         <v>2.8568571428571428</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="E9" s="13">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="E9" s="12">
         <f>AVERAGE(population!H2:H36)</f>
         <v>931.2285714285714</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="H9" s="13">
+      <c r="F9" s="12"/>
+      <c r="H9" s="12">
         <f>AVERAGE(population!I11)</f>
         <v>78.03</v>
       </c>
-      <c r="I9" s="13"/>
+      <c r="I9" s="12"/>
       <c r="L9" s="6" t="s">
         <v>66</v>
       </c>
@@ -6298,12 +6464,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A8:C8"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
@@ -6316,6 +6476,12 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6324,7 +6490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881F210B-A9CA-4D54-9D0F-4913621E3B09}">
-  <dimension ref="A3:M76"/>
+  <dimension ref="A2:N76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
@@ -6332,47 +6498,56 @@
     <col min="5" max="5" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.109375" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
@@ -6380,25 +6555,25 @@
         <v>92</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>91</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>88</v>
       </c>
@@ -6411,23 +6586,26 @@
       <c r="F5" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>95</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>70</v>
       </c>
@@ -6440,23 +6618,27 @@
       <c r="F6" s="10">
         <v>177710</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="10">
+        <v>202871</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="10">
         <v>960981</v>
       </c>
-      <c r="J6" s="10">
+      <c r="K6" s="10">
         <v>2710051</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.03</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>72</v>
       </c>
@@ -6469,23 +6651,27 @@
       <c r="F7" s="10">
         <v>42138631</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="10">
+        <v>42442146</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="10">
+      <c r="J7" s="10">
         <v>561997</v>
       </c>
-      <c r="J7" s="10">
+      <c r="K7" s="10">
         <v>529037</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
@@ -6498,23 +6684,27 @@
       <c r="F8" s="10">
         <v>669815</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="10">
+        <v>713912</v>
+      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="10">
+      <c r="J8" s="10">
         <v>23578175</v>
       </c>
-      <c r="J8" s="10">
+      <c r="K8" s="10">
         <v>37552529</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>76</v>
       </c>
@@ -6527,23 +6717,27 @@
       <c r="F9" s="10">
         <v>15266133</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="10">
+        <v>15939443</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="10">
+      <c r="J9" s="10">
         <v>20059666</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="10">
         <v>52537899</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
@@ -6556,23 +6750,27 @@
       <c r="F10" s="10">
         <v>49821295</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="10">
+        <v>54278157</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="10">
         <v>6996124</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="10">
         <v>34951234</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.11</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>48</v>
       </c>
@@ -6585,23 +6783,27 @@
       <c r="F11" s="10">
         <v>474787</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="10">
+        <v>580663</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="10">
         <v>20234706</v>
       </c>
-      <c r="J11" s="10">
+      <c r="K11" s="10">
         <v>33877297</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.11</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>89</v>
       </c>
@@ -6614,948 +6816,1068 @@
       <c r="F12" s="10">
         <v>12712303</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="G12" s="10">
+        <v>12832895</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="10">
+      <c r="J12" s="10">
         <v>34949729</v>
       </c>
-      <c r="J12" s="10">
+      <c r="K12" s="10">
         <v>37189229</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="M12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>2.58</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E13" s="9" t="s">
         <v>72</v>
       </c>
       <c r="F13" s="10">
         <v>149949</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="G13" s="10">
+        <v>193760</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="10">
+      <c r="J13" s="10">
         <v>182580</v>
       </c>
-      <c r="J13" s="10">
+      <c r="K13" s="10">
         <v>60331</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>2.58</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E14" s="9" t="s">
         <v>74</v>
       </c>
       <c r="F14" s="10">
         <v>92946</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="10">
+        <v>150301</v>
+      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="10">
+      <c r="J14" s="10">
         <v>3091169</v>
       </c>
-      <c r="J14" s="10">
+      <c r="K14" s="10">
         <v>7025583</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>8.6</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E15" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="10">
         <v>7800615</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="G15" s="10">
+        <v>8887326</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="10">
+      <c r="J15" s="10">
         <v>12905780</v>
       </c>
-      <c r="J15" s="10">
+      <c r="K15" s="10">
         <v>944727</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="M15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>8.6</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E16" s="9" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="10">
         <v>719405</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="G16" s="10">
+        <v>739140</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I16" s="10">
+      <c r="J16" s="10">
         <v>4388756</v>
       </c>
-      <c r="J16" s="10">
+      <c r="K16" s="10">
         <v>26780526</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.09</v>
       </c>
     </row>
-    <row r="17" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="10">
         <v>28948432</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="G17" s="10">
+        <v>31491260</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <v>25712811</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <v>34670817</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="M17" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E18" s="9" t="s">
         <v>45</v>
       </c>
       <c r="F18" s="10">
         <v>11856728</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="G18" s="10">
+        <v>13494734</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <v>151726</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <v>455962</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="M18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>2.11</v>
       </c>
     </row>
-    <row r="19" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E19" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F19" s="10">
         <v>3382729</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="G19" s="10">
+        <v>3481873</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="10">
         <v>28219075</v>
       </c>
-      <c r="J19" s="10">
+      <c r="K19" s="10">
         <v>56361702</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="M19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>2.11</v>
       </c>
     </row>
-    <row r="20" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="10">
         <v>5900640</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="G20" s="10">
+        <v>6640662</v>
+      </c>
+      <c r="H20" s="10"/>
+      <c r="I20" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I20" s="10">
+      <c r="J20" s="10">
         <v>822132</v>
       </c>
-      <c r="J20" s="10">
+      <c r="K20" s="10">
         <v>1899624</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E21" s="9" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="10">
         <v>16057819</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="G21" s="10">
+        <v>16930315</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="10">
+      <c r="J21" s="10">
         <v>313446</v>
       </c>
-      <c r="J21" s="10">
+      <c r="K21" s="10">
         <v>1069165</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="M21" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E22" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="10">
         <v>30128640</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="G22" s="10">
+        <v>30966657</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="10">
+      <c r="J22" s="10">
         <v>17080776</v>
       </c>
-      <c r="J22" s="10">
+      <c r="K22" s="10">
         <v>51540236</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E23" s="9" t="s">
         <v>35</v>
       </c>
       <c r="F23" s="10">
         <v>17378649</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="G23" s="10">
+        <v>16027412</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="10">
+      <c r="J23" s="10">
         <v>3414106</v>
       </c>
-      <c r="J23" s="10">
+      <c r="K23" s="10">
         <v>9134820</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="M23" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.02</v>
       </c>
     </row>
-    <row r="24" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E24" s="9" t="s">
         <v>76</v>
       </c>
       <c r="F24" s="10">
         <v>31350</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="G24" s="10">
+        <v>33123</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I24" s="10">
+      <c r="J24" s="10">
         <v>50308</v>
       </c>
-      <c r="J24" s="10">
+      <c r="K24" s="10">
         <v>14121</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>1.39</v>
       </c>
     </row>
-    <row r="25" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E25" s="9" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="10">
         <v>35014503</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="G25" s="10">
+        <v>37612306</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I25" s="10">
+      <c r="J25" s="10">
         <v>573741</v>
       </c>
-      <c r="J25" s="10">
+      <c r="K25" s="10">
         <v>1406861</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="M25" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>1.39</v>
       </c>
     </row>
-    <row r="26" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E26" s="9" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="10">
         <v>54131277</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="G26" s="10">
+        <v>58243056</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="10">
+      <c r="J26" s="10">
         <v>29134060</v>
       </c>
-      <c r="J26" s="10">
+      <c r="K26" s="10">
         <v>62213676</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="M26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>0.12</v>
       </c>
     </row>
-    <row r="27" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E27" s="9" t="s">
         <v>56</v>
       </c>
       <c r="F27" s="10">
         <v>1280219</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="G27" s="10">
+        <v>1290171</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="10">
+      <c r="J27" s="10">
         <v>44470455</v>
       </c>
-      <c r="J27" s="10">
+      <c r="K27" s="10">
         <v>155111022</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="M27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>0.12</v>
       </c>
     </row>
-    <row r="28" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E28" s="9" t="s">
         <v>54</v>
       </c>
       <c r="F28" s="10">
         <v>1475057</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="G28" s="10">
+        <v>1491832</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="10">
+      <c r="J28" s="10">
         <v>50827531</v>
       </c>
-      <c r="J28" s="10">
+      <c r="K28" s="10">
         <v>61545441</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>4.99</v>
       </c>
     </row>
-    <row r="29" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E29" s="9" t="s">
         <v>66</v>
       </c>
       <c r="F29" s="10">
         <v>541867</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="G29" s="10">
+        <v>555339</v>
+      </c>
+      <c r="H29" s="10"/>
+      <c r="I29" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="10">
+      <c r="J29" s="10">
         <v>906309</v>
       </c>
-      <c r="J29" s="10">
+      <c r="K29" s="10">
         <v>551414</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>4.99</v>
       </c>
     </row>
-    <row r="30" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E30" s="9" t="s">
         <v>58</v>
       </c>
       <c r="F30" s="10">
         <v>953853</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="G30" s="10">
+        <v>1024649</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="10">
+      <c r="J30" s="10">
         <v>11729609</v>
       </c>
-      <c r="J30" s="10">
+      <c r="K30" s="10">
         <v>92075028</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="M30" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>2.09</v>
       </c>
     </row>
-    <row r="31" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E31" s="9" t="s">
         <v>33</v>
       </c>
       <c r="F31" s="10">
         <v>20762082</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="G31" s="10">
+        <v>21212136</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="10">
+      <c r="J31" s="10">
         <v>850123</v>
       </c>
-      <c r="J31" s="10">
+      <c r="K31" s="10">
         <v>394341</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="M31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>2.09</v>
       </c>
     </row>
-    <row r="32" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E32" s="9" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="10">
         <v>635442</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="G32" s="10">
+        <v>612511</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I32" s="10">
+      <c r="J32" s="10">
         <v>135533</v>
       </c>
-      <c r="J32" s="10">
+      <c r="K32" s="10">
         <v>244411</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="M32" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="33" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E33" s="9" t="s">
         <v>41</v>
       </c>
       <c r="F33" s="10">
         <v>13103873</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="G33" s="10">
+        <v>14639465</v>
+      </c>
+      <c r="H33" s="10"/>
+      <c r="I33" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="10">
+      <c r="J33" s="10">
         <v>5936538</v>
       </c>
-      <c r="J33" s="10">
+      <c r="K33" s="10">
         <v>19603658</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="M33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="34" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E34" s="9" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="10">
         <v>32997440</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="G34" s="10">
+        <v>35550997</v>
+      </c>
+      <c r="H34" s="10"/>
+      <c r="I34" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="10">
+      <c r="J34" s="10">
         <v>7929292</v>
       </c>
-      <c r="J34" s="10">
+      <c r="K34" s="10">
         <v>25036946</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="M34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>1.04</v>
       </c>
     </row>
-    <row r="35" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="F35" s="10">
         <v>287507</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="G35" s="10">
+        <v>323070</v>
+      </c>
+      <c r="H35" s="10"/>
+      <c r="I35" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="10">
+      <c r="J35" s="10">
         <v>595036</v>
       </c>
-      <c r="J35" s="10">
+      <c r="K35" s="10">
         <v>2368971</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="M35" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>1.04</v>
       </c>
     </row>
-    <row r="36" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E36" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="10">
         <v>36009055</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="G36" s="10">
+        <v>36137975</v>
+      </c>
+      <c r="H36" s="10"/>
+      <c r="I36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="10">
+      <c r="J36" s="10">
         <v>688704</v>
       </c>
-      <c r="J36" s="10">
+      <c r="K36" s="10">
         <v>6167805</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>2.72</v>
       </c>
     </row>
-    <row r="37" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E37" s="9" t="s">
         <v>52</v>
       </c>
       <c r="F37" s="10">
         <v>1799541</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="G37" s="10">
+        <v>1874376</v>
+      </c>
+      <c r="H37" s="10"/>
+      <c r="I37" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="10">
+      <c r="J37" s="10">
         <v>159829</v>
       </c>
-      <c r="J37" s="10">
+      <c r="K37" s="10">
         <v>183024</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="M37" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>2.72</v>
       </c>
     </row>
-    <row r="38" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E38" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="10">
         <v>95331831</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="G38" s="10">
+        <v>104480510</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I38" s="10">
+      <c r="J38" s="10">
         <v>15932171</v>
       </c>
-      <c r="J38" s="10">
+      <c r="K38" s="10">
         <v>17445506</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="M38" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>5.05</v>
       </c>
     </row>
-    <row r="39" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E39" s="9" t="s">
         <v>48</v>
       </c>
       <c r="F39" s="10">
         <v>4948519</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="G39" s="10">
+        <v>5137773</v>
+      </c>
+      <c r="H39" s="10"/>
+      <c r="I39" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I39" s="10">
+      <c r="J39" s="10">
         <v>373542974</v>
       </c>
-      <c r="J39" s="10">
+      <c r="K39" s="10">
         <v>833652994</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="M39" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>5.05</v>
       </c>
     </row>
-    <row r="40" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E40" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F40" s="10">
         <v>44467088</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="G40" s="10">
+        <v>46809027</v>
+      </c>
+      <c r="H40" s="10"/>
+      <c r="M40" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>2.76</v>
       </c>
     </row>
-    <row r="41" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="5:14" x14ac:dyDescent="0.3">
       <c r="E41" s="9" t="s">
         <v>89</v>
       </c>
       <c r="F41" s="10">
         <v>587447730</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="G41" s="10">
+        <v>623021843</v>
+      </c>
+      <c r="H41" s="10"/>
+      <c r="M41" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>2.76</v>
       </c>
     </row>
-    <row r="42" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L42" s="9" t="s">
+    <row r="42" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M42" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>0.01</v>
       </c>
     </row>
-    <row r="43" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L43" s="11" t="s">
+    <row r="43" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M43" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>0.01</v>
       </c>
     </row>
-    <row r="44" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L44" s="9" t="s">
+    <row r="44" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L45" s="11" t="s">
+    <row r="45" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M45" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L46" s="9" t="s">
+    <row r="46" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M46" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="47" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L47" s="11" t="s">
+    <row r="47" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M47" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="48" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="L48" s="9" t="s">
+    <row r="48" spans="5:14" x14ac:dyDescent="0.3">
+      <c r="M48" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>0.21</v>
       </c>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L49" s="11" t="s">
+    <row r="49" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M49" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M49">
+      <c r="N49">
         <v>0.21</v>
       </c>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L50" s="9" t="s">
+    <row r="50" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M50" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M50">
+      <c r="N50">
         <v>0.25</v>
       </c>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L51" s="11" t="s">
+    <row r="51" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M51" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>0.25</v>
       </c>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L52" s="9" t="s">
+    <row r="52" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M52" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>0.09</v>
       </c>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L53" s="11" t="s">
+    <row r="53" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M53" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>0.09</v>
       </c>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L54" s="9" t="s">
+    <row r="54" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M54" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>0.16</v>
       </c>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L55" s="11" t="s">
+    <row r="55" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M55" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>0.16</v>
       </c>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L56" s="9" t="s">
+    <row r="56" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M56" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>3.47</v>
       </c>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L57" s="11" t="s">
+    <row r="57" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M57" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>3.47</v>
       </c>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L58" s="9" t="s">
+    <row r="58" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M58" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>0.1</v>
       </c>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L59" s="11" t="s">
+    <row r="59" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M59" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>0.1</v>
       </c>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L60" s="9" t="s">
+    <row r="60" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M60" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>2.29</v>
       </c>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L61" s="11" t="s">
+    <row r="61" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M61" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>2.29</v>
       </c>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L62" s="9" t="s">
+    <row r="62" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M62" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>5.66</v>
       </c>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L63" s="11" t="s">
+    <row r="63" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>5.66</v>
       </c>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L64" s="9" t="s">
+    <row r="64" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M64" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>0.05</v>
       </c>
     </row>
-    <row r="65" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L65" s="11" t="s">
+    <row r="65" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M65" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>0.05</v>
       </c>
     </row>
-    <row r="66" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L66" s="9" t="s">
+    <row r="66" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M66" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>5.96</v>
       </c>
     </row>
-    <row r="67" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L67" s="11" t="s">
+    <row r="67" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M67" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>5.96</v>
       </c>
     </row>
-    <row r="68" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L68" s="9" t="s">
+    <row r="68" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M68" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>0.3</v>
       </c>
     </row>
-    <row r="69" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L69" s="11" t="s">
+    <row r="69" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M69" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>0.3</v>
       </c>
     </row>
-    <row r="70" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L70" s="9" t="s">
+    <row r="70" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M70" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>16.5</v>
       </c>
     </row>
-    <row r="71" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L71" s="11" t="s">
+    <row r="71" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M71" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>16.5</v>
       </c>
     </row>
-    <row r="72" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L72" s="9" t="s">
+    <row r="72" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M72" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>0.83</v>
       </c>
     </row>
-    <row r="73" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L73" s="11" t="s">
+    <row r="73" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M73" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>0.83</v>
       </c>
     </row>
-    <row r="74" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L74" s="9" t="s">
+    <row r="74" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M74" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>7.54</v>
       </c>
     </row>
-    <row r="75" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L75" s="11" t="s">
+    <row r="75" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M75" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="M75">
+      <c r="N75">
         <v>7.54</v>
       </c>
     </row>
-    <row r="76" spans="12:13" x14ac:dyDescent="0.3">
-      <c r="L76" s="9" t="s">
+    <row r="76" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="M76" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="M76">
+      <c r="N76">
         <v>99.99</v>
       </c>
     </row>
